--- a/output/tables/2025/tabla2_variables_fuente.xlsx
+++ b/output/tables/2025/tabla2_variables_fuente.xlsx
@@ -559,7 +559,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="55.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="7.71" hidden="0" customWidth="1"/>
@@ -618,7 +618,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="n">
-        <v>9.09090909090909</v>
+        <v>9.09</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -664,7 +664,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>11.1111111111111</v>
+        <v>11.11</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -710,7 +710,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>14.2857142857143</v>
+        <v>14.29</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -733,7 +733,7 @@
         <v>11</v>
       </c>
       <c r="B8" t="n">
-        <v>16.6666666666667</v>
+        <v>16.67</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
@@ -756,7 +756,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>18.1818181818182</v>
+        <v>18.18</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -802,7 +802,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="n">
-        <v>22.2222222222222</v>
+        <v>22.22</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -848,7 +848,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>27.2727272727273</v>
+        <v>27.27</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -871,7 +871,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>28.5714285714286</v>
+        <v>28.57</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -917,7 +917,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="n">
-        <v>33.3333333333333</v>
+        <v>33.33</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -940,7 +940,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="n">
-        <v>36.3636363636364</v>
+        <v>36.36</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
@@ -1009,7 +1009,7 @@
         <v>11</v>
       </c>
       <c r="B20" t="n">
-        <v>42.8571428571429</v>
+        <v>42.86</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -1032,7 +1032,7 @@
         <v>11</v>
       </c>
       <c r="B21" t="n">
-        <v>44.4444444444444</v>
+        <v>44.44</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -1055,7 +1055,7 @@
         <v>11</v>
       </c>
       <c r="B22" t="n">
-        <v>45.4545454545455</v>
+        <v>45.45</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -1101,7 +1101,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="n">
-        <v>54.5454545454545</v>
+        <v>54.55</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -1124,7 +1124,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="n">
-        <v>55.5555555555556</v>
+        <v>55.56</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
@@ -1147,7 +1147,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="n">
-        <v>57.1428571428571</v>
+        <v>57.14</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -1216,7 +1216,7 @@
         <v>11</v>
       </c>
       <c r="B29" t="n">
-        <v>63.6363636363636</v>
+        <v>63.64</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
@@ -1239,7 +1239,7 @@
         <v>11</v>
       </c>
       <c r="B30" t="n">
-        <v>66.6666666666667</v>
+        <v>66.67</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -1285,7 +1285,7 @@
         <v>11</v>
       </c>
       <c r="B32" t="n">
-        <v>71.4285714285714</v>
+        <v>71.43</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
@@ -1308,7 +1308,7 @@
         <v>11</v>
       </c>
       <c r="B33" t="n">
-        <v>72.7272727272727</v>
+        <v>72.73</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -1354,7 +1354,7 @@
         <v>11</v>
       </c>
       <c r="B35" t="n">
-        <v>77.7777777777778</v>
+        <v>77.78</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
@@ -1400,7 +1400,7 @@
         <v>11</v>
       </c>
       <c r="B37" t="n">
-        <v>81.8181818181818</v>
+        <v>81.82</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
@@ -1423,7 +1423,7 @@
         <v>11</v>
       </c>
       <c r="B38" t="n">
-        <v>83.3333333333333</v>
+        <v>83.33</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -1446,7 +1446,7 @@
         <v>11</v>
       </c>
       <c r="B39" t="n">
-        <v>85.7142857142857</v>
+        <v>85.71</v>
       </c>
       <c r="C39" t="s">
         <v>12</v>
@@ -1492,7 +1492,7 @@
         <v>11</v>
       </c>
       <c r="B41" t="n">
-        <v>88.8888888888889</v>
+        <v>88.89</v>
       </c>
       <c r="C41" t="s">
         <v>12</v>
@@ -1538,7 +1538,7 @@
         <v>11</v>
       </c>
       <c r="B43" t="n">
-        <v>90.9090909090909</v>
+        <v>90.91</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -1557,232 +1557,256 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
+      <c r="A44" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="C44" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" t="n">
+      <c r="C44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="2" t="n">
         <v>918924</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="2" t="n">
         <v>6.92</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="2" t="n">
         <v>6.92</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2" t="n">
+      <c r="A45" t="s">
+        <v>13</v>
+      </c>
+      <c r="B45" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
+      <c r="C45" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" t="n">
+        <v>4140827</v>
+      </c>
+      <c r="E45" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="F45" t="n">
+        <v>31.59</v>
+      </c>
+      <c r="G45" t="n">
+        <v>31.59</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
         <v>13</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
         <v>12</v>
       </c>
       <c r="D46" t="n">
-        <v>4140827</v>
+        <v>5574634</v>
       </c>
       <c r="E46" t="n">
-        <v>31.59</v>
+        <v>42.52</v>
       </c>
       <c r="F46" t="n">
-        <v>31.59</v>
+        <v>42.52</v>
       </c>
       <c r="G46" t="n">
-        <v>31.59</v>
+        <v>74.11</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
+      <c r="A47" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B47" t="n">
-        <v>50</v>
-      </c>
-      <c r="C47" t="s">
-        <v>12</v>
-      </c>
-      <c r="D47" t="n">
-        <v>5574634</v>
-      </c>
-      <c r="E47" t="n">
-        <v>42.52</v>
-      </c>
-      <c r="F47" t="n">
-        <v>42.52</v>
-      </c>
-      <c r="G47" t="n">
-        <v>74.11</v>
+      <c r="B47" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>3394070</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="n">
+        <v>10297783</v>
+      </c>
+      <c r="E48" t="n">
+        <v>77.59</v>
+      </c>
+      <c r="F48" t="n">
+        <v>77.59</v>
+      </c>
+      <c r="G48" t="n">
+        <v>77.59</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" t="n">
+        <v>50</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1763276</v>
+      </c>
+      <c r="E49" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="F49" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="G49" t="n">
+        <v>90.88</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="C48" t="s">
-        <v>12</v>
-      </c>
-      <c r="D48" t="n">
-        <v>3394070</v>
-      </c>
-      <c r="E48" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="F48" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="G48" t="n">
+      <c r="C50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>1211052</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>9.12</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>9.12</v>
+      </c>
+      <c r="G50" s="2" t="n">
         <v>100</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>14</v>
-      </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" t="s">
-        <v>12</v>
-      </c>
-      <c r="D50" t="n">
-        <v>10297783</v>
-      </c>
-      <c r="E50" t="n">
-        <v>77.59</v>
-      </c>
-      <c r="F50" t="n">
-        <v>77.59</v>
-      </c>
-      <c r="G50" t="n">
-        <v>77.59</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B51" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C51" t="s">
         <v>12</v>
       </c>
       <c r="D51" t="n">
-        <v>1763276</v>
+        <v>1824758</v>
       </c>
       <c r="E51" t="n">
-        <v>13.29</v>
+        <v>13.73</v>
       </c>
       <c r="F51" t="n">
-        <v>13.29</v>
+        <v>13.73</v>
       </c>
       <c r="G51" t="n">
-        <v>90.88</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B52" t="n">
-        <v>100</v>
+        <v>7.69</v>
       </c>
       <c r="C52" t="s">
         <v>12</v>
       </c>
       <c r="D52" t="n">
-        <v>1211052</v>
+        <v>267128</v>
       </c>
       <c r="E52" t="n">
-        <v>9.12</v>
+        <v>2.01</v>
       </c>
       <c r="F52" t="n">
-        <v>9.12</v>
+        <v>2.01</v>
       </c>
       <c r="G52" t="n">
-        <v>100</v>
+        <v>15.74</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" t="n">
+        <v>301494</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F53" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G53" t="n">
+        <v>18.01</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
         <v>15</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="C54" t="s">
         <v>12</v>
       </c>
       <c r="D54" t="n">
-        <v>1824758</v>
+        <v>243848</v>
       </c>
       <c r="E54" t="n">
-        <v>13.73</v>
+        <v>1.83</v>
       </c>
       <c r="F54" t="n">
-        <v>13.73</v>
+        <v>1.83</v>
       </c>
       <c r="G54" t="n">
-        <v>13.73</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="55">
@@ -1790,22 +1814,22 @@
         <v>15</v>
       </c>
       <c r="B55" t="n">
-        <v>7.69230769230769</v>
+        <v>10</v>
       </c>
       <c r="C55" t="s">
         <v>12</v>
       </c>
       <c r="D55" t="n">
-        <v>267128</v>
+        <v>214615</v>
       </c>
       <c r="E55" t="n">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="F55" t="n">
-        <v>2.01</v>
+        <v>1.61</v>
       </c>
       <c r="G55" t="n">
-        <v>15.74</v>
+        <v>21.46</v>
       </c>
     </row>
     <row r="56">
@@ -1813,22 +1837,22 @@
         <v>15</v>
       </c>
       <c r="B56" t="n">
-        <v>8.33333333333333</v>
+        <v>11.11</v>
       </c>
       <c r="C56" t="s">
         <v>12</v>
       </c>
       <c r="D56" t="n">
-        <v>301494</v>
+        <v>140033</v>
       </c>
       <c r="E56" t="n">
-        <v>2.27</v>
+        <v>1.05</v>
       </c>
       <c r="F56" t="n">
-        <v>2.27</v>
+        <v>1.05</v>
       </c>
       <c r="G56" t="n">
-        <v>18.01</v>
+        <v>22.51</v>
       </c>
     </row>
     <row r="57">
@@ -1836,22 +1860,22 @@
         <v>15</v>
       </c>
       <c r="B57" t="n">
-        <v>9.09090909090909</v>
+        <v>12.5</v>
       </c>
       <c r="C57" t="s">
         <v>12</v>
       </c>
       <c r="D57" t="n">
-        <v>243848</v>
+        <v>88207</v>
       </c>
       <c r="E57" t="n">
-        <v>1.83</v>
+        <v>0.66</v>
       </c>
       <c r="F57" t="n">
-        <v>1.83</v>
+        <v>0.66</v>
       </c>
       <c r="G57" t="n">
-        <v>19.84</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="58">
@@ -1859,22 +1883,22 @@
         <v>15</v>
       </c>
       <c r="B58" t="n">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="C58" t="s">
         <v>12</v>
       </c>
       <c r="D58" t="n">
-        <v>214615</v>
+        <v>50648</v>
       </c>
       <c r="E58" t="n">
-        <v>1.61</v>
+        <v>0.38</v>
       </c>
       <c r="F58" t="n">
-        <v>1.61</v>
+        <v>0.38</v>
       </c>
       <c r="G58" t="n">
-        <v>21.46</v>
+        <v>23.56</v>
       </c>
     </row>
     <row r="59">
@@ -1882,22 +1906,22 @@
         <v>15</v>
       </c>
       <c r="B59" t="n">
-        <v>11.1111111111111</v>
+        <v>15.38</v>
       </c>
       <c r="C59" t="s">
         <v>12</v>
       </c>
       <c r="D59" t="n">
-        <v>140033</v>
+        <v>266899</v>
       </c>
       <c r="E59" t="n">
-        <v>1.05</v>
+        <v>2.01</v>
       </c>
       <c r="F59" t="n">
-        <v>1.05</v>
+        <v>2.01</v>
       </c>
       <c r="G59" t="n">
-        <v>22.51</v>
+        <v>25.57</v>
       </c>
     </row>
     <row r="60">
@@ -1905,22 +1929,22 @@
         <v>15</v>
       </c>
       <c r="B60" t="n">
-        <v>12.5</v>
+        <v>16.67</v>
       </c>
       <c r="C60" t="s">
         <v>12</v>
       </c>
       <c r="D60" t="n">
-        <v>88207</v>
+        <v>325959</v>
       </c>
       <c r="E60" t="n">
-        <v>0.66</v>
+        <v>2.45</v>
       </c>
       <c r="F60" t="n">
-        <v>0.66</v>
+        <v>2.45</v>
       </c>
       <c r="G60" t="n">
-        <v>23.18</v>
+        <v>28.02</v>
       </c>
     </row>
     <row r="61">
@@ -1928,22 +1952,22 @@
         <v>15</v>
       </c>
       <c r="B61" t="n">
-        <v>14.2857142857143</v>
+        <v>18.18</v>
       </c>
       <c r="C61" t="s">
         <v>12</v>
       </c>
       <c r="D61" t="n">
-        <v>50648</v>
+        <v>232941</v>
       </c>
       <c r="E61" t="n">
-        <v>0.38</v>
+        <v>1.75</v>
       </c>
       <c r="F61" t="n">
-        <v>0.38</v>
+        <v>1.75</v>
       </c>
       <c r="G61" t="n">
-        <v>23.56</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="62">
@@ -1951,22 +1975,22 @@
         <v>15</v>
       </c>
       <c r="B62" t="n">
-        <v>15.3846153846154</v>
+        <v>20</v>
       </c>
       <c r="C62" t="s">
         <v>12</v>
       </c>
       <c r="D62" t="n">
-        <v>266899</v>
+        <v>199499</v>
       </c>
       <c r="E62" t="n">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="F62" t="n">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="G62" t="n">
-        <v>25.57</v>
+        <v>31.27</v>
       </c>
     </row>
     <row r="63">
@@ -1974,22 +1998,22 @@
         <v>15</v>
       </c>
       <c r="B63" t="n">
-        <v>16.6666666666667</v>
+        <v>22.22</v>
       </c>
       <c r="C63" t="s">
         <v>12</v>
       </c>
       <c r="D63" t="n">
-        <v>325959</v>
+        <v>131534</v>
       </c>
       <c r="E63" t="n">
-        <v>2.45</v>
+        <v>0.99</v>
       </c>
       <c r="F63" t="n">
-        <v>2.45</v>
+        <v>0.99</v>
       </c>
       <c r="G63" t="n">
-        <v>28.02</v>
+        <v>32.26</v>
       </c>
     </row>
     <row r="64">
@@ -1997,22 +2021,22 @@
         <v>15</v>
       </c>
       <c r="B64" t="n">
-        <v>18.1818181818182</v>
+        <v>23.08</v>
       </c>
       <c r="C64" t="s">
         <v>12</v>
       </c>
       <c r="D64" t="n">
-        <v>232941</v>
+        <v>265504</v>
       </c>
       <c r="E64" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>29.77</v>
+        <v>34.26</v>
       </c>
     </row>
     <row r="65">
@@ -2020,22 +2044,22 @@
         <v>15</v>
       </c>
       <c r="B65" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C65" t="s">
         <v>12</v>
       </c>
       <c r="D65" t="n">
-        <v>199499</v>
+        <v>371449</v>
       </c>
       <c r="E65" t="n">
-        <v>1.5</v>
+        <v>2.79</v>
       </c>
       <c r="F65" t="n">
-        <v>1.5</v>
+        <v>2.79</v>
       </c>
       <c r="G65" t="n">
-        <v>31.27</v>
+        <v>37.05</v>
       </c>
     </row>
     <row r="66">
@@ -2043,22 +2067,22 @@
         <v>15</v>
       </c>
       <c r="B66" t="n">
-        <v>22.2222222222222</v>
+        <v>27.27</v>
       </c>
       <c r="C66" t="s">
         <v>12</v>
       </c>
       <c r="D66" t="n">
-        <v>131534</v>
+        <v>226839</v>
       </c>
       <c r="E66" t="n">
-        <v>0.99</v>
+        <v>1.71</v>
       </c>
       <c r="F66" t="n">
-        <v>0.99</v>
+        <v>1.71</v>
       </c>
       <c r="G66" t="n">
-        <v>32.26</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="67">
@@ -2066,22 +2090,22 @@
         <v>15</v>
       </c>
       <c r="B67" t="n">
-        <v>23.0769230769231</v>
+        <v>28.57</v>
       </c>
       <c r="C67" t="s">
         <v>12</v>
       </c>
       <c r="D67" t="n">
-        <v>265504</v>
+        <v>44530</v>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>0.34</v>
       </c>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>0.34</v>
       </c>
       <c r="G67" t="n">
-        <v>34.26</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="68">
@@ -2089,22 +2113,22 @@
         <v>15</v>
       </c>
       <c r="B68" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
       </c>
       <c r="D68" t="n">
-        <v>371449</v>
+        <v>197133</v>
       </c>
       <c r="E68" t="n">
-        <v>2.79</v>
+        <v>1.48</v>
       </c>
       <c r="F68" t="n">
-        <v>2.79</v>
+        <v>1.48</v>
       </c>
       <c r="G68" t="n">
-        <v>37.05</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="69">
@@ -2112,22 +2136,22 @@
         <v>15</v>
       </c>
       <c r="B69" t="n">
-        <v>27.2727272727273</v>
+        <v>30.77</v>
       </c>
       <c r="C69" t="s">
         <v>12</v>
       </c>
       <c r="D69" t="n">
-        <v>226839</v>
+        <v>272739</v>
       </c>
       <c r="E69" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="F69" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="G69" t="n">
-        <v>38.76</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="70">
@@ -2135,22 +2159,22 @@
         <v>15</v>
       </c>
       <c r="B70" t="n">
-        <v>28.5714285714286</v>
+        <v>33.33</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
       </c>
       <c r="D70" t="n">
-        <v>44530</v>
+        <v>404592</v>
       </c>
       <c r="E70" t="n">
-        <v>0.34</v>
+        <v>3.04</v>
       </c>
       <c r="F70" t="n">
-        <v>0.34</v>
+        <v>3.04</v>
       </c>
       <c r="G70" t="n">
-        <v>39.1</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="71">
@@ -2158,22 +2182,22 @@
         <v>15</v>
       </c>
       <c r="B71" t="n">
-        <v>30</v>
+        <v>36.36</v>
       </c>
       <c r="C71" t="s">
         <v>12</v>
       </c>
       <c r="D71" t="n">
-        <v>197133</v>
+        <v>215735</v>
       </c>
       <c r="E71" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="F71" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="G71" t="n">
-        <v>40.58</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="72">
@@ -2181,22 +2205,22 @@
         <v>15</v>
       </c>
       <c r="B72" t="n">
-        <v>30.7692307692308</v>
+        <v>37.5</v>
       </c>
       <c r="C72" t="s">
         <v>12</v>
       </c>
       <c r="D72" t="n">
-        <v>272739</v>
+        <v>65768</v>
       </c>
       <c r="E72" t="n">
-        <v>2.05</v>
+        <v>0.49</v>
       </c>
       <c r="F72" t="n">
-        <v>2.05</v>
+        <v>0.49</v>
       </c>
       <c r="G72" t="n">
-        <v>42.63</v>
+        <v>47.79</v>
       </c>
     </row>
     <row r="73">
@@ -2204,22 +2228,22 @@
         <v>15</v>
       </c>
       <c r="B73" t="n">
-        <v>33.3333333333333</v>
+        <v>38.46</v>
       </c>
       <c r="C73" t="s">
         <v>12</v>
       </c>
       <c r="D73" t="n">
-        <v>404592</v>
+        <v>268833</v>
       </c>
       <c r="E73" t="n">
-        <v>3.04</v>
+        <v>2.02</v>
       </c>
       <c r="F73" t="n">
-        <v>3.04</v>
+        <v>2.02</v>
       </c>
       <c r="G73" t="n">
-        <v>45.68</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="74">
@@ -2227,22 +2251,22 @@
         <v>15</v>
       </c>
       <c r="B74" t="n">
-        <v>36.3636363636364</v>
+        <v>40</v>
       </c>
       <c r="C74" t="s">
         <v>12</v>
       </c>
       <c r="D74" t="n">
-        <v>215735</v>
+        <v>197838</v>
       </c>
       <c r="E74" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="F74" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="G74" t="n">
-        <v>47.3</v>
+        <v>51.31</v>
       </c>
     </row>
     <row r="75">
@@ -2250,22 +2274,22 @@
         <v>15</v>
       </c>
       <c r="B75" t="n">
-        <v>37.5</v>
+        <v>41.67</v>
       </c>
       <c r="C75" t="s">
         <v>12</v>
       </c>
       <c r="D75" t="n">
-        <v>65768</v>
+        <v>296644</v>
       </c>
       <c r="E75" t="n">
-        <v>0.49</v>
+        <v>2.23</v>
       </c>
       <c r="F75" t="n">
-        <v>0.49</v>
+        <v>2.23</v>
       </c>
       <c r="G75" t="n">
-        <v>47.79</v>
+        <v>53.54</v>
       </c>
     </row>
     <row r="76">
@@ -2273,22 +2297,22 @@
         <v>15</v>
       </c>
       <c r="B76" t="n">
-        <v>38.4615384615385</v>
+        <v>42.86</v>
       </c>
       <c r="C76" t="s">
         <v>12</v>
       </c>
       <c r="D76" t="n">
-        <v>268833</v>
+        <v>34752</v>
       </c>
       <c r="E76" t="n">
-        <v>2.02</v>
+        <v>0.26</v>
       </c>
       <c r="F76" t="n">
-        <v>2.02</v>
+        <v>0.26</v>
       </c>
       <c r="G76" t="n">
-        <v>49.82</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="77">
@@ -2296,22 +2320,22 @@
         <v>15</v>
       </c>
       <c r="B77" t="n">
-        <v>40</v>
+        <v>44.44</v>
       </c>
       <c r="C77" t="s">
         <v>12</v>
       </c>
       <c r="D77" t="n">
-        <v>197838</v>
+        <v>101606</v>
       </c>
       <c r="E77" t="n">
-        <v>1.49</v>
+        <v>0.76</v>
       </c>
       <c r="F77" t="n">
-        <v>1.49</v>
+        <v>0.76</v>
       </c>
       <c r="G77" t="n">
-        <v>51.31</v>
+        <v>54.56</v>
       </c>
     </row>
     <row r="78">
@@ -2319,22 +2343,22 @@
         <v>15</v>
       </c>
       <c r="B78" t="n">
-        <v>41.6666666666667</v>
+        <v>45.45</v>
       </c>
       <c r="C78" t="s">
         <v>12</v>
       </c>
       <c r="D78" t="n">
-        <v>296644</v>
+        <v>220048</v>
       </c>
       <c r="E78" t="n">
-        <v>2.23</v>
+        <v>1.66</v>
       </c>
       <c r="F78" t="n">
-        <v>2.23</v>
+        <v>1.66</v>
       </c>
       <c r="G78" t="n">
-        <v>53.54</v>
+        <v>56.22</v>
       </c>
     </row>
     <row r="79">
@@ -2342,22 +2366,22 @@
         <v>15</v>
       </c>
       <c r="B79" t="n">
-        <v>42.8571428571429</v>
+        <v>46.15</v>
       </c>
       <c r="C79" t="s">
         <v>12</v>
       </c>
       <c r="D79" t="n">
-        <v>34752</v>
+        <v>255399</v>
       </c>
       <c r="E79" t="n">
-        <v>0.26</v>
+        <v>1.92</v>
       </c>
       <c r="F79" t="n">
-        <v>0.26</v>
+        <v>1.92</v>
       </c>
       <c r="G79" t="n">
-        <v>53.8</v>
+        <v>58.14</v>
       </c>
     </row>
     <row r="80">
@@ -2365,22 +2389,22 @@
         <v>15</v>
       </c>
       <c r="B80" t="n">
-        <v>44.4444444444444</v>
+        <v>50</v>
       </c>
       <c r="C80" t="s">
         <v>12</v>
       </c>
       <c r="D80" t="n">
-        <v>101606</v>
+        <v>563017</v>
       </c>
       <c r="E80" t="n">
-        <v>0.76</v>
+        <v>4.24</v>
       </c>
       <c r="F80" t="n">
-        <v>0.76</v>
+        <v>4.24</v>
       </c>
       <c r="G80" t="n">
-        <v>54.56</v>
+        <v>62.38</v>
       </c>
     </row>
     <row r="81">
@@ -2388,22 +2412,22 @@
         <v>15</v>
       </c>
       <c r="B81" t="n">
-        <v>45.4545454545455</v>
+        <v>53.85</v>
       </c>
       <c r="C81" t="s">
         <v>12</v>
       </c>
       <c r="D81" t="n">
-        <v>220048</v>
+        <v>290589</v>
       </c>
       <c r="E81" t="n">
-        <v>1.66</v>
+        <v>2.19</v>
       </c>
       <c r="F81" t="n">
-        <v>1.66</v>
+        <v>2.19</v>
       </c>
       <c r="G81" t="n">
-        <v>56.22</v>
+        <v>64.56</v>
       </c>
     </row>
     <row r="82">
@@ -2411,22 +2435,22 @@
         <v>15</v>
       </c>
       <c r="B82" t="n">
-        <v>46.1538461538462</v>
+        <v>54.55</v>
       </c>
       <c r="C82" t="s">
         <v>12</v>
       </c>
       <c r="D82" t="n">
-        <v>255399</v>
+        <v>230077</v>
       </c>
       <c r="E82" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="F82" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="G82" t="n">
-        <v>58.14</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="83">
@@ -2434,22 +2458,22 @@
         <v>15</v>
       </c>
       <c r="B83" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="C83" t="s">
         <v>12</v>
       </c>
       <c r="D83" t="n">
-        <v>563017</v>
+        <v>107622</v>
       </c>
       <c r="E83" t="n">
-        <v>4.24</v>
+        <v>0.81</v>
       </c>
       <c r="F83" t="n">
-        <v>4.24</v>
+        <v>0.81</v>
       </c>
       <c r="G83" t="n">
-        <v>62.38</v>
+        <v>67.11</v>
       </c>
     </row>
     <row r="84">
@@ -2457,22 +2481,22 @@
         <v>15</v>
       </c>
       <c r="B84" t="n">
-        <v>53.8461538461538</v>
+        <v>57.14</v>
       </c>
       <c r="C84" t="s">
         <v>12</v>
       </c>
       <c r="D84" t="n">
-        <v>290589</v>
+        <v>34854</v>
       </c>
       <c r="E84" t="n">
-        <v>2.19</v>
+        <v>0.26</v>
       </c>
       <c r="F84" t="n">
-        <v>2.19</v>
+        <v>0.26</v>
       </c>
       <c r="G84" t="n">
-        <v>64.56</v>
+        <v>67.37</v>
       </c>
     </row>
     <row r="85">
@@ -2480,22 +2504,22 @@
         <v>15</v>
       </c>
       <c r="B85" t="n">
-        <v>54.5454545454545</v>
+        <v>58.33</v>
       </c>
       <c r="C85" t="s">
         <v>12</v>
       </c>
       <c r="D85" t="n">
-        <v>230077</v>
+        <v>308641</v>
       </c>
       <c r="E85" t="n">
-        <v>1.73</v>
+        <v>2.32</v>
       </c>
       <c r="F85" t="n">
-        <v>1.73</v>
+        <v>2.32</v>
       </c>
       <c r="G85" t="n">
-        <v>66.3</v>
+        <v>69.69</v>
       </c>
     </row>
     <row r="86">
@@ -2503,22 +2527,22 @@
         <v>15</v>
       </c>
       <c r="B86" t="n">
-        <v>55.5555555555556</v>
+        <v>60</v>
       </c>
       <c r="C86" t="s">
         <v>12</v>
       </c>
       <c r="D86" t="n">
-        <v>107622</v>
+        <v>182526</v>
       </c>
       <c r="E86" t="n">
-        <v>0.81</v>
+        <v>1.37</v>
       </c>
       <c r="F86" t="n">
-        <v>0.81</v>
+        <v>1.37</v>
       </c>
       <c r="G86" t="n">
-        <v>67.11</v>
+        <v>71.06</v>
       </c>
     </row>
     <row r="87">
@@ -2526,22 +2550,22 @@
         <v>15</v>
       </c>
       <c r="B87" t="n">
-        <v>57.1428571428571</v>
+        <v>61.54</v>
       </c>
       <c r="C87" t="s">
         <v>12</v>
       </c>
       <c r="D87" t="n">
-        <v>34854</v>
+        <v>304420</v>
       </c>
       <c r="E87" t="n">
-        <v>0.26</v>
+        <v>2.29</v>
       </c>
       <c r="F87" t="n">
-        <v>0.26</v>
+        <v>2.29</v>
       </c>
       <c r="G87" t="n">
-        <v>67.37</v>
+        <v>73.35</v>
       </c>
     </row>
     <row r="88">
@@ -2549,22 +2573,22 @@
         <v>15</v>
       </c>
       <c r="B88" t="n">
-        <v>58.3333333333333</v>
+        <v>62.5</v>
       </c>
       <c r="C88" t="s">
         <v>12</v>
       </c>
       <c r="D88" t="n">
-        <v>308641</v>
+        <v>53695</v>
       </c>
       <c r="E88" t="n">
-        <v>2.32</v>
+        <v>0.4</v>
       </c>
       <c r="F88" t="n">
-        <v>2.32</v>
+        <v>0.4</v>
       </c>
       <c r="G88" t="n">
-        <v>69.69</v>
+        <v>73.76</v>
       </c>
     </row>
     <row r="89">
@@ -2572,22 +2596,22 @@
         <v>15</v>
       </c>
       <c r="B89" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="C89" t="s">
         <v>12</v>
       </c>
       <c r="D89" t="n">
-        <v>182526</v>
+        <v>232015</v>
       </c>
       <c r="E89" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="F89" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="G89" t="n">
-        <v>71.06</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="90">
@@ -2595,22 +2619,22 @@
         <v>15</v>
       </c>
       <c r="B90" t="n">
-        <v>61.5384615384615</v>
+        <v>66.67</v>
       </c>
       <c r="C90" t="s">
         <v>12</v>
       </c>
       <c r="D90" t="n">
-        <v>304420</v>
+        <v>415027</v>
       </c>
       <c r="E90" t="n">
-        <v>2.29</v>
+        <v>3.12</v>
       </c>
       <c r="F90" t="n">
-        <v>2.29</v>
+        <v>3.12</v>
       </c>
       <c r="G90" t="n">
-        <v>73.35</v>
+        <v>78.63</v>
       </c>
     </row>
     <row r="91">
@@ -2618,22 +2642,22 @@
         <v>15</v>
       </c>
       <c r="B91" t="n">
-        <v>62.5</v>
+        <v>69.23</v>
       </c>
       <c r="C91" t="s">
         <v>12</v>
       </c>
       <c r="D91" t="n">
-        <v>53695</v>
+        <v>278666</v>
       </c>
       <c r="E91" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="F91" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="G91" t="n">
-        <v>73.76</v>
+        <v>80.72</v>
       </c>
     </row>
     <row r="92">
@@ -2641,22 +2665,22 @@
         <v>15</v>
       </c>
       <c r="B92" t="n">
-        <v>63.6363636363636</v>
+        <v>70</v>
       </c>
       <c r="C92" t="s">
         <v>12</v>
       </c>
       <c r="D92" t="n">
-        <v>232015</v>
+        <v>167594</v>
       </c>
       <c r="E92" t="n">
-        <v>1.75</v>
+        <v>1.26</v>
       </c>
       <c r="F92" t="n">
-        <v>1.75</v>
+        <v>1.26</v>
       </c>
       <c r="G92" t="n">
-        <v>75.5</v>
+        <v>81.99</v>
       </c>
     </row>
     <row r="93">
@@ -2664,22 +2688,22 @@
         <v>15</v>
       </c>
       <c r="B93" t="n">
-        <v>66.6666666666667</v>
+        <v>71.43</v>
       </c>
       <c r="C93" t="s">
         <v>12</v>
       </c>
       <c r="D93" t="n">
-        <v>415027</v>
+        <v>26189</v>
       </c>
       <c r="E93" t="n">
-        <v>3.12</v>
+        <v>0.2</v>
       </c>
       <c r="F93" t="n">
-        <v>3.12</v>
+        <v>0.2</v>
       </c>
       <c r="G93" t="n">
-        <v>78.63</v>
+        <v>82.18</v>
       </c>
     </row>
     <row r="94">
@@ -2687,22 +2711,22 @@
         <v>15</v>
       </c>
       <c r="B94" t="n">
-        <v>69.2307692307692</v>
+        <v>72.73</v>
       </c>
       <c r="C94" t="s">
         <v>12</v>
       </c>
       <c r="D94" t="n">
-        <v>278666</v>
+        <v>191508</v>
       </c>
       <c r="E94" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="F94" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G94" t="n">
-        <v>80.72</v>
+        <v>83.62</v>
       </c>
     </row>
     <row r="95">
@@ -2710,22 +2734,22 @@
         <v>15</v>
       </c>
       <c r="B95" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C95" t="s">
         <v>12</v>
       </c>
       <c r="D95" t="n">
-        <v>167594</v>
+        <v>293168</v>
       </c>
       <c r="E95" t="n">
-        <v>1.26</v>
+        <v>2.21</v>
       </c>
       <c r="F95" t="n">
-        <v>1.26</v>
+        <v>2.21</v>
       </c>
       <c r="G95" t="n">
-        <v>81.99</v>
+        <v>85.83</v>
       </c>
     </row>
     <row r="96">
@@ -2733,22 +2757,22 @@
         <v>15</v>
       </c>
       <c r="B96" t="n">
-        <v>71.4285714285714</v>
+        <v>76.92</v>
       </c>
       <c r="C96" t="s">
         <v>12</v>
       </c>
       <c r="D96" t="n">
-        <v>26189</v>
+        <v>246761</v>
       </c>
       <c r="E96" t="n">
-        <v>0.2</v>
+        <v>1.86</v>
       </c>
       <c r="F96" t="n">
-        <v>0.2</v>
+        <v>1.86</v>
       </c>
       <c r="G96" t="n">
-        <v>82.18</v>
+        <v>87.69</v>
       </c>
     </row>
     <row r="97">
@@ -2756,22 +2780,22 @@
         <v>15</v>
       </c>
       <c r="B97" t="n">
-        <v>72.7272727272727</v>
+        <v>77.78</v>
       </c>
       <c r="C97" t="s">
         <v>12</v>
       </c>
       <c r="D97" t="n">
-        <v>191508</v>
+        <v>93784</v>
       </c>
       <c r="E97" t="n">
-        <v>1.44</v>
+        <v>0.71</v>
       </c>
       <c r="F97" t="n">
-        <v>1.44</v>
+        <v>0.71</v>
       </c>
       <c r="G97" t="n">
-        <v>83.62</v>
+        <v>88.39</v>
       </c>
     </row>
     <row r="98">
@@ -2779,22 +2803,22 @@
         <v>15</v>
       </c>
       <c r="B98" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C98" t="s">
         <v>12</v>
       </c>
       <c r="D98" t="n">
-        <v>293168</v>
+        <v>138238</v>
       </c>
       <c r="E98" t="n">
-        <v>2.21</v>
+        <v>1.04</v>
       </c>
       <c r="F98" t="n">
-        <v>2.21</v>
+        <v>1.04</v>
       </c>
       <c r="G98" t="n">
-        <v>85.83</v>
+        <v>89.43</v>
       </c>
     </row>
     <row r="99">
@@ -2802,22 +2826,22 @@
         <v>15</v>
       </c>
       <c r="B99" t="n">
-        <v>76.9230769230769</v>
+        <v>81.82</v>
       </c>
       <c r="C99" t="s">
         <v>12</v>
       </c>
       <c r="D99" t="n">
-        <v>246761</v>
+        <v>134103</v>
       </c>
       <c r="E99" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="F99" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="G99" t="n">
-        <v>87.69</v>
+        <v>90.44</v>
       </c>
     </row>
     <row r="100">
@@ -2825,22 +2849,22 @@
         <v>15</v>
       </c>
       <c r="B100" t="n">
-        <v>77.7777777777778</v>
+        <v>83.33</v>
       </c>
       <c r="C100" t="s">
         <v>12</v>
       </c>
       <c r="D100" t="n">
-        <v>93784</v>
+        <v>182802</v>
       </c>
       <c r="E100" t="n">
-        <v>0.71</v>
+        <v>1.38</v>
       </c>
       <c r="F100" t="n">
-        <v>0.71</v>
+        <v>1.38</v>
       </c>
       <c r="G100" t="n">
-        <v>88.39</v>
+        <v>91.82</v>
       </c>
     </row>
     <row r="101">
@@ -2848,22 +2872,22 @@
         <v>15</v>
       </c>
       <c r="B101" t="n">
-        <v>80</v>
+        <v>84.62</v>
       </c>
       <c r="C101" t="s">
         <v>12</v>
       </c>
       <c r="D101" t="n">
-        <v>138238</v>
+        <v>213226</v>
       </c>
       <c r="E101" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="F101" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="G101" t="n">
-        <v>89.43</v>
+        <v>93.42</v>
       </c>
     </row>
     <row r="102">
@@ -2871,22 +2895,22 @@
         <v>15</v>
       </c>
       <c r="B102" t="n">
-        <v>81.8181818181818</v>
+        <v>85.71</v>
       </c>
       <c r="C102" t="s">
         <v>12</v>
       </c>
       <c r="D102" t="n">
-        <v>134103</v>
+        <v>18694</v>
       </c>
       <c r="E102" t="n">
-        <v>1.01</v>
+        <v>0.14</v>
       </c>
       <c r="F102" t="n">
-        <v>1.01</v>
+        <v>0.14</v>
       </c>
       <c r="G102" t="n">
-        <v>90.44</v>
+        <v>93.56</v>
       </c>
     </row>
     <row r="103">
@@ -2894,22 +2918,22 @@
         <v>15</v>
       </c>
       <c r="B103" t="n">
-        <v>83.3333333333333</v>
+        <v>87.5</v>
       </c>
       <c r="C103" t="s">
         <v>12</v>
       </c>
       <c r="D103" t="n">
-        <v>182802</v>
+        <v>31560</v>
       </c>
       <c r="E103" t="n">
-        <v>1.38</v>
+        <v>0.24</v>
       </c>
       <c r="F103" t="n">
-        <v>1.38</v>
+        <v>0.24</v>
       </c>
       <c r="G103" t="n">
-        <v>91.82</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="104">
@@ -2917,22 +2941,22 @@
         <v>15</v>
       </c>
       <c r="B104" t="n">
-        <v>84.6153846153846</v>
+        <v>88.89</v>
       </c>
       <c r="C104" t="s">
         <v>12</v>
       </c>
       <c r="D104" t="n">
-        <v>213226</v>
+        <v>50099</v>
       </c>
       <c r="E104" t="n">
-        <v>1.6</v>
+        <v>0.38</v>
       </c>
       <c r="F104" t="n">
-        <v>1.6</v>
+        <v>0.38</v>
       </c>
       <c r="G104" t="n">
-        <v>93.42</v>
+        <v>94.18</v>
       </c>
     </row>
     <row r="105">
@@ -2940,22 +2964,22 @@
         <v>15</v>
       </c>
       <c r="B105" t="n">
-        <v>85.7142857142857</v>
+        <v>90</v>
       </c>
       <c r="C105" t="s">
         <v>12</v>
       </c>
       <c r="D105" t="n">
-        <v>18694</v>
+        <v>93401</v>
       </c>
       <c r="E105" t="n">
-        <v>0.14</v>
+        <v>0.7</v>
       </c>
       <c r="F105" t="n">
-        <v>0.14</v>
+        <v>0.7</v>
       </c>
       <c r="G105" t="n">
-        <v>93.56</v>
+        <v>94.88</v>
       </c>
     </row>
     <row r="106">
@@ -2963,22 +2987,22 @@
         <v>15</v>
       </c>
       <c r="B106" t="n">
-        <v>87.5</v>
+        <v>90.91</v>
       </c>
       <c r="C106" t="s">
         <v>12</v>
       </c>
       <c r="D106" t="n">
-        <v>31560</v>
+        <v>95380</v>
       </c>
       <c r="E106" t="n">
-        <v>0.24</v>
+        <v>0.72</v>
       </c>
       <c r="F106" t="n">
-        <v>0.24</v>
+        <v>0.72</v>
       </c>
       <c r="G106" t="n">
-        <v>93.8</v>
+        <v>95.6</v>
       </c>
     </row>
     <row r="107">
@@ -2986,22 +3010,22 @@
         <v>15</v>
       </c>
       <c r="B107" t="n">
-        <v>88.8888888888889</v>
+        <v>91.67</v>
       </c>
       <c r="C107" t="s">
         <v>12</v>
       </c>
       <c r="D107" t="n">
-        <v>50099</v>
+        <v>119820</v>
       </c>
       <c r="E107" t="n">
-        <v>0.38</v>
+        <v>0.9</v>
       </c>
       <c r="F107" t="n">
-        <v>0.38</v>
+        <v>0.9</v>
       </c>
       <c r="G107" t="n">
-        <v>94.18</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="108">
@@ -3009,152 +3033,160 @@
         <v>15</v>
       </c>
       <c r="B108" t="n">
-        <v>90</v>
+        <v>92.31</v>
       </c>
       <c r="C108" t="s">
         <v>12</v>
       </c>
       <c r="D108" t="n">
-        <v>93401</v>
+        <v>172469</v>
       </c>
       <c r="E108" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="F108" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="G108" t="n">
-        <v>94.88</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="n">
-        <v>90.9090909090909</v>
-      </c>
-      <c r="C109" t="s">
-        <v>12</v>
-      </c>
-      <c r="D109" t="n">
-        <v>95380</v>
-      </c>
-      <c r="E109" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G109" t="n">
-        <v>95.6</v>
+      <c r="A109" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>292921</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B110" t="n">
-        <v>91.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="C110" t="s">
         <v>12</v>
       </c>
       <c r="D110" t="n">
-        <v>119820</v>
+        <v>1088781</v>
       </c>
       <c r="E110" t="n">
-        <v>0.9</v>
+        <v>8.2</v>
       </c>
       <c r="F110" t="n">
-        <v>0.9</v>
+        <v>8.2</v>
       </c>
       <c r="G110" t="n">
-        <v>96.5</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B111" t="n">
-        <v>92.3076923076923</v>
+        <v>11.11</v>
       </c>
       <c r="C111" t="s">
         <v>12</v>
       </c>
       <c r="D111" t="n">
-        <v>172469</v>
+        <v>3103365</v>
       </c>
       <c r="E111" t="n">
-        <v>1.3</v>
+        <v>23.38</v>
       </c>
       <c r="F111" t="n">
-        <v>1.3</v>
+        <v>23.38</v>
       </c>
       <c r="G111" t="n">
-        <v>97.8</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B112" t="n">
-        <v>100</v>
+        <v>22.22</v>
       </c>
       <c r="C112" t="s">
         <v>12</v>
       </c>
       <c r="D112" t="n">
-        <v>292921</v>
+        <v>3556934</v>
       </c>
       <c r="E112" t="n">
-        <v>2.2</v>
+        <v>26.8</v>
       </c>
       <c r="F112" t="n">
-        <v>2.2</v>
+        <v>26.8</v>
       </c>
       <c r="G112" t="n">
-        <v>100</v>
+        <v>58.38</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
+      <c r="A113" t="s">
+        <v>16</v>
+      </c>
+      <c r="B113" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="C113" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2631062</v>
+      </c>
+      <c r="E113" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="F113" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="G113" t="n">
+        <v>78.21</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
         <v>16</v>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>44.44</v>
       </c>
       <c r="C114" t="s">
         <v>12</v>
       </c>
       <c r="D114" t="n">
-        <v>1088781</v>
+        <v>1528379</v>
       </c>
       <c r="E114" t="n">
-        <v>8.2</v>
+        <v>11.52</v>
       </c>
       <c r="F114" t="n">
-        <v>8.2</v>
+        <v>11.52</v>
       </c>
       <c r="G114" t="n">
-        <v>8.2</v>
+        <v>89.72</v>
       </c>
     </row>
     <row r="115">
@@ -3162,22 +3194,22 @@
         <v>16</v>
       </c>
       <c r="B115" t="n">
-        <v>11.1111111111111</v>
+        <v>55.56</v>
       </c>
       <c r="C115" t="s">
         <v>12</v>
       </c>
       <c r="D115" t="n">
-        <v>3103365</v>
+        <v>782192</v>
       </c>
       <c r="E115" t="n">
-        <v>23.38</v>
+        <v>5.89</v>
       </c>
       <c r="F115" t="n">
-        <v>23.38</v>
+        <v>5.89</v>
       </c>
       <c r="G115" t="n">
-        <v>31.59</v>
+        <v>95.62</v>
       </c>
     </row>
     <row r="116">
@@ -3185,22 +3217,22 @@
         <v>16</v>
       </c>
       <c r="B116" t="n">
-        <v>22.2222222222222</v>
+        <v>66.67</v>
       </c>
       <c r="C116" t="s">
         <v>12</v>
       </c>
       <c r="D116" t="n">
-        <v>3556934</v>
+        <v>381157</v>
       </c>
       <c r="E116" t="n">
-        <v>26.8</v>
+        <v>2.87</v>
       </c>
       <c r="F116" t="n">
-        <v>26.8</v>
+        <v>2.87</v>
       </c>
       <c r="G116" t="n">
-        <v>58.38</v>
+        <v>98.49</v>
       </c>
     </row>
     <row r="117">
@@ -3208,22 +3240,22 @@
         <v>16</v>
       </c>
       <c r="B117" t="n">
-        <v>33.3333333333333</v>
+        <v>77.78</v>
       </c>
       <c r="C117" t="s">
         <v>12</v>
       </c>
       <c r="D117" t="n">
-        <v>2631062</v>
+        <v>162624</v>
       </c>
       <c r="E117" t="n">
-        <v>19.82</v>
+        <v>1.23</v>
       </c>
       <c r="F117" t="n">
-        <v>19.82</v>
+        <v>1.23</v>
       </c>
       <c r="G117" t="n">
-        <v>78.21</v>
+        <v>99.71</v>
       </c>
     </row>
     <row r="118">
@@ -3231,175 +3263,183 @@
         <v>16</v>
       </c>
       <c r="B118" t="n">
-        <v>44.4444444444444</v>
+        <v>88.89</v>
       </c>
       <c r="C118" t="s">
         <v>12</v>
       </c>
       <c r="D118" t="n">
-        <v>1528379</v>
+        <v>36088</v>
       </c>
       <c r="E118" t="n">
-        <v>11.52</v>
+        <v>0.27</v>
       </c>
       <c r="F118" t="n">
-        <v>11.52</v>
+        <v>0.27</v>
       </c>
       <c r="G118" t="n">
-        <v>89.72</v>
+        <v>99.99</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="s">
+      <c r="A119" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B119" t="n">
-        <v>55.5555555555556</v>
-      </c>
-      <c r="C119" t="s">
-        <v>12</v>
-      </c>
-      <c r="D119" t="n">
-        <v>782192</v>
-      </c>
-      <c r="E119" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="F119" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="G119" t="n">
-        <v>95.62</v>
+      <c r="B119" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>1931</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B120" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="C120" t="s">
         <v>12</v>
       </c>
       <c r="D120" t="n">
-        <v>381157</v>
+        <v>3267358</v>
       </c>
       <c r="E120" t="n">
-        <v>2.87</v>
+        <v>25.31</v>
       </c>
       <c r="F120" t="n">
-        <v>2.87</v>
+        <v>25.31</v>
       </c>
       <c r="G120" t="n">
-        <v>98.49</v>
+        <v>25.31</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B121" t="n">
-        <v>77.7777777777778</v>
+        <v>12.5</v>
       </c>
       <c r="C121" t="s">
         <v>12</v>
       </c>
       <c r="D121" t="n">
-        <v>162624</v>
+        <v>3603876</v>
       </c>
       <c r="E121" t="n">
-        <v>1.23</v>
+        <v>27.91</v>
       </c>
       <c r="F121" t="n">
-        <v>1.23</v>
+        <v>27.91</v>
       </c>
       <c r="G121" t="n">
-        <v>99.71</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B122" t="n">
-        <v>88.8888888888889</v>
+        <v>25</v>
       </c>
       <c r="C122" t="s">
         <v>12</v>
       </c>
       <c r="D122" t="n">
-        <v>36088</v>
+        <v>2923576</v>
       </c>
       <c r="E122" t="n">
-        <v>0.27</v>
+        <v>22.64</v>
       </c>
       <c r="F122" t="n">
-        <v>0.27</v>
+        <v>22.64</v>
       </c>
       <c r="G122" t="n">
-        <v>99.99</v>
+        <v>75.86</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B123" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="C123" t="s">
         <v>12</v>
       </c>
       <c r="D123" t="n">
-        <v>1931</v>
+        <v>1706426</v>
       </c>
       <c r="E123" t="n">
-        <v>0.01</v>
+        <v>13.22</v>
       </c>
       <c r="F123" t="n">
-        <v>0.01</v>
+        <v>13.22</v>
       </c>
       <c r="G123" t="n">
-        <v>100</v>
+        <v>89.08</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
+      <c r="A124" t="s">
+        <v>17</v>
+      </c>
+      <c r="B124" t="n">
+        <v>50</v>
+      </c>
+      <c r="C124" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" t="n">
+        <v>805341</v>
+      </c>
+      <c r="E124" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="F124" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="G124" t="n">
+        <v>95.32</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
         <v>17</v>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="C125" t="s">
         <v>12</v>
       </c>
       <c r="D125" t="n">
-        <v>3267358</v>
+        <v>418863</v>
       </c>
       <c r="E125" t="n">
-        <v>25.31</v>
+        <v>3.24</v>
       </c>
       <c r="F125" t="n">
-        <v>25.31</v>
+        <v>3.24</v>
       </c>
       <c r="G125" t="n">
-        <v>25.31</v>
+        <v>98.56</v>
       </c>
     </row>
     <row r="126">
@@ -3407,22 +3447,22 @@
         <v>17</v>
       </c>
       <c r="B126" t="n">
-        <v>12.5</v>
+        <v>75</v>
       </c>
       <c r="C126" t="s">
         <v>12</v>
       </c>
       <c r="D126" t="n">
-        <v>3603876</v>
+        <v>152816</v>
       </c>
       <c r="E126" t="n">
-        <v>27.91</v>
+        <v>1.18</v>
       </c>
       <c r="F126" t="n">
-        <v>27.91</v>
+        <v>1.18</v>
       </c>
       <c r="G126" t="n">
-        <v>53.22</v>
+        <v>99.74</v>
       </c>
     </row>
     <row r="127">
@@ -3430,157 +3470,157 @@
         <v>17</v>
       </c>
       <c r="B127" t="n">
-        <v>25</v>
+        <v>87.5</v>
       </c>
       <c r="C127" t="s">
         <v>12</v>
       </c>
       <c r="D127" t="n">
-        <v>2923576</v>
+        <v>29418</v>
       </c>
       <c r="E127" t="n">
-        <v>22.64</v>
+        <v>0.23</v>
       </c>
       <c r="F127" t="n">
-        <v>22.64</v>
+        <v>0.23</v>
       </c>
       <c r="G127" t="n">
-        <v>75.86</v>
+        <v>99.97</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="s">
+      <c r="A128" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B128" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="C128" t="s">
-        <v>12</v>
-      </c>
-      <c r="D128" t="n">
-        <v>1706426</v>
-      </c>
-      <c r="E128" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="F128" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="G128" t="n">
-        <v>89.08</v>
+      <c r="B128" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>3517</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B129" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="C129" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D129" t="n">
-        <v>805341</v>
+        <v>3735069</v>
       </c>
       <c r="E129" t="n">
-        <v>6.24</v>
+        <v>28.09</v>
       </c>
       <c r="F129" t="n">
-        <v>6.24</v>
+        <v>28.09</v>
       </c>
       <c r="G129" t="n">
-        <v>95.32</v>
+        <v>28.09</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B130" t="n">
-        <v>62.5</v>
+        <v>2</v>
       </c>
       <c r="C130" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D130" t="n">
-        <v>418863</v>
+        <v>4754124</v>
       </c>
       <c r="E130" t="n">
-        <v>3.24</v>
+        <v>35.76</v>
       </c>
       <c r="F130" t="n">
-        <v>3.24</v>
+        <v>35.76</v>
       </c>
       <c r="G130" t="n">
-        <v>98.56</v>
+        <v>63.85</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B131" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="C131" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D131" t="n">
-        <v>152816</v>
+        <v>4781865</v>
       </c>
       <c r="E131" t="n">
-        <v>1.18</v>
+        <v>35.96</v>
       </c>
       <c r="F131" t="n">
-        <v>1.18</v>
+        <v>35.96</v>
       </c>
       <c r="G131" t="n">
-        <v>99.74</v>
+        <v>99.81</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B132" t="n">
-        <v>87.5</v>
+        <v>85</v>
       </c>
       <c r="C132" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D132" t="n">
-        <v>29418</v>
+        <v>24831</v>
       </c>
       <c r="E132" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="F132" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="G132" t="n">
-        <v>99.97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B133" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D133" t="n">
-        <v>3517</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
         <v>100</v>
@@ -3588,91 +3628,99 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B134" s="2"/>
-      <c r="C134" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="D134" s="2" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="E134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
+      <c r="F134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B135" t="n">
         <v>1</v>
       </c>
       <c r="C135" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D135" t="n">
-        <v>3735069</v>
+        <v>3724967</v>
       </c>
       <c r="E135" t="n">
-        <v>28.09</v>
+        <v>28.02</v>
       </c>
       <c r="F135" t="n">
-        <v>28.09</v>
+        <v>28.02</v>
       </c>
       <c r="G135" t="n">
-        <v>28.09</v>
+        <v>28.02</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B136" t="n">
         <v>2</v>
       </c>
       <c r="C136" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D136" t="n">
-        <v>4754124</v>
+        <v>4365275</v>
       </c>
       <c r="E136" t="n">
-        <v>35.76</v>
+        <v>32.83</v>
       </c>
       <c r="F136" t="n">
-        <v>35.76</v>
+        <v>32.83</v>
       </c>
       <c r="G136" t="n">
-        <v>63.85</v>
+        <v>60.85</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B137" t="n">
         <v>3</v>
       </c>
       <c r="C137" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D137" t="n">
-        <v>4781865</v>
+        <v>5016942</v>
       </c>
       <c r="E137" t="n">
-        <v>35.96</v>
+        <v>37.73</v>
       </c>
       <c r="F137" t="n">
-        <v>35.96</v>
+        <v>37.73</v>
       </c>
       <c r="G137" t="n">
-        <v>99.81</v>
+        <v>98.58</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B138" t="n">
         <v>85</v>
@@ -3681,21 +3729,21 @@
         <v>22</v>
       </c>
       <c r="D138" t="n">
-        <v>24831</v>
+        <v>186527</v>
       </c>
       <c r="E138" t="n">
-        <v>0.19</v>
+        <v>1.4</v>
       </c>
       <c r="F138" t="n">
-        <v>0.19</v>
+        <v>1.4</v>
       </c>
       <c r="G138" t="n">
-        <v>100</v>
+        <v>99.98</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B139" t="n">
         <v>88</v>
@@ -3704,587 +3752,619 @@
         <v>23</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>2136</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G139" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="s">
-        <v>18</v>
-      </c>
-      <c r="B140" t="n">
+      <c r="A140" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B140" s="2" t="n">
         <v>99</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D140" t="n">
-        <v>169</v>
-      </c>
-      <c r="E140" t="n">
+      <c r="D140" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="E140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F140" t="n">
+      <c r="F140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G140" t="n">
+      <c r="G140" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
-      <c r="D141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" s="2"/>
-      <c r="G141" s="2"/>
+      <c r="A141" t="s">
+        <v>29</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="s">
+        <v>30</v>
+      </c>
+      <c r="D141" t="n">
+        <v>4582770</v>
+      </c>
+      <c r="E141" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="F141" t="n">
+        <v>34.47</v>
+      </c>
+      <c r="G141" t="n">
+        <v>34.47</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C142" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D142" t="n">
-        <v>3724967</v>
+        <v>4490784</v>
       </c>
       <c r="E142" t="n">
-        <v>28.02</v>
+        <v>33.78</v>
       </c>
       <c r="F142" t="n">
-        <v>28.02</v>
+        <v>33.78</v>
       </c>
       <c r="G142" t="n">
-        <v>28.02</v>
+        <v>68.24</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C143" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D143" t="n">
-        <v>4365275</v>
+        <v>4197523</v>
       </c>
       <c r="E143" t="n">
-        <v>32.83</v>
+        <v>31.57</v>
       </c>
       <c r="F143" t="n">
-        <v>32.83</v>
+        <v>31.57</v>
       </c>
       <c r="G143" t="n">
-        <v>60.85</v>
+        <v>99.81</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B144" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="C144" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D144" t="n">
-        <v>5016942</v>
+        <v>23947</v>
       </c>
       <c r="E144" t="n">
-        <v>37.73</v>
+        <v>0.18</v>
       </c>
       <c r="F144" t="n">
-        <v>37.73</v>
+        <v>0.18</v>
       </c>
       <c r="G144" t="n">
-        <v>98.58</v>
+        <v>99.99</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B145" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C145" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D145" t="n">
-        <v>186527</v>
+        <v>866</v>
       </c>
       <c r="E145" t="n">
-        <v>1.4</v>
+        <v>0.01</v>
       </c>
       <c r="F145" t="n">
-        <v>1.4</v>
+        <v>0.01</v>
       </c>
       <c r="G145" t="n">
-        <v>99.98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="s">
-        <v>25</v>
-      </c>
-      <c r="B146" t="n">
-        <v>88</v>
-      </c>
-      <c r="C146" t="s">
-        <v>23</v>
-      </c>
-      <c r="D146" t="n">
-        <v>2136</v>
-      </c>
-      <c r="E146" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F146" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G146" t="n">
+      <c r="A146" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B147" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="C147" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D147" t="n">
-        <v>211</v>
+        <v>5835997</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>43.89</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>43.89</v>
       </c>
       <c r="G147" t="n">
-        <v>100</v>
+        <v>43.89</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
-      <c r="D148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E148" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F148" s="2"/>
-      <c r="G148" s="2"/>
+      <c r="A148" t="s">
+        <v>33</v>
+      </c>
+      <c r="B148" t="n">
+        <v>2</v>
+      </c>
+      <c r="C148" t="s">
+        <v>35</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3008974</v>
+      </c>
+      <c r="E148" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="F148" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="G148" t="n">
+        <v>66.52</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C149" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D149" t="n">
-        <v>4582770</v>
+        <v>3969197</v>
       </c>
       <c r="E149" t="n">
-        <v>34.47</v>
+        <v>29.85</v>
       </c>
       <c r="F149" t="n">
-        <v>34.47</v>
+        <v>29.85</v>
       </c>
       <c r="G149" t="n">
-        <v>34.47</v>
+        <v>96.38</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B150" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D150" t="n">
-        <v>4490784</v>
+        <v>441454</v>
       </c>
       <c r="E150" t="n">
-        <v>33.78</v>
+        <v>3.32</v>
       </c>
       <c r="F150" t="n">
-        <v>33.78</v>
+        <v>3.32</v>
       </c>
       <c r="G150" t="n">
-        <v>68.24</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C151" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D151" t="n">
-        <v>4197523</v>
+        <v>17381</v>
       </c>
       <c r="E151" t="n">
-        <v>31.57</v>
+        <v>0.13</v>
       </c>
       <c r="F151" t="n">
-        <v>31.57</v>
+        <v>0.13</v>
       </c>
       <c r="G151" t="n">
-        <v>99.81</v>
+        <v>99.83</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="s">
-        <v>29</v>
-      </c>
-      <c r="B152" t="n">
-        <v>85</v>
-      </c>
-      <c r="C152" t="s">
-        <v>22</v>
-      </c>
-      <c r="D152" t="n">
-        <v>23947</v>
-      </c>
-      <c r="E152" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="F152" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G152" t="n">
-        <v>99.99</v>
+      <c r="A152" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>23055</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B153" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="C153" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D153" t="n">
-        <v>866</v>
+        <v>3798414</v>
       </c>
       <c r="E153" t="n">
-        <v>0.01</v>
+        <v>28.57</v>
       </c>
       <c r="F153" t="n">
-        <v>0.01</v>
+        <v>28.57</v>
       </c>
       <c r="G153" t="n">
-        <v>100</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B154" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="C154" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D154" t="n">
-        <v>169</v>
+        <v>4536571</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>34.12</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>34.12</v>
       </c>
       <c r="G154" t="n">
-        <v>100</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B155" s="2"/>
-      <c r="C155" s="2"/>
-      <c r="D155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F155" s="2"/>
-      <c r="G155" s="2"/>
+      <c r="A155" t="s">
+        <v>40</v>
+      </c>
+      <c r="B155" t="n">
+        <v>3</v>
+      </c>
+      <c r="C155" t="s">
+        <v>43</v>
+      </c>
+      <c r="D155" t="n">
+        <v>4954688</v>
+      </c>
+      <c r="E155" t="n">
+        <v>37.26</v>
+      </c>
+      <c r="F155" t="n">
+        <v>37.26</v>
+      </c>
+      <c r="G155" t="n">
+        <v>99.95</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B156" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="C156" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D156" t="n">
-        <v>5835997</v>
+        <v>6216</v>
       </c>
       <c r="E156" t="n">
-        <v>43.89</v>
+        <v>0.05</v>
       </c>
       <c r="F156" t="n">
-        <v>43.89</v>
+        <v>0.05</v>
       </c>
       <c r="G156" t="n">
-        <v>43.89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B157" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="C157" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D157" t="n">
-        <v>3008974</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>22.63</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>22.63</v>
+        <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>66.52</v>
+        <v>100</v>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="s">
-        <v>33</v>
-      </c>
-      <c r="B158" t="n">
-        <v>3</v>
-      </c>
-      <c r="C158" t="s">
-        <v>36</v>
-      </c>
-      <c r="D158" t="n">
-        <v>3969197</v>
-      </c>
-      <c r="E158" t="n">
-        <v>29.85</v>
-      </c>
-      <c r="F158" t="n">
-        <v>29.85</v>
-      </c>
-      <c r="G158" t="n">
-        <v>96.38</v>
+      <c r="A158" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B159" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C159" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D159" t="n">
-        <v>441454</v>
+        <v>6295807</v>
       </c>
       <c r="E159" t="n">
-        <v>3.32</v>
+        <v>47.35</v>
       </c>
       <c r="F159" t="n">
-        <v>3.32</v>
+        <v>47.35</v>
       </c>
       <c r="G159" t="n">
-        <v>99.7</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B160" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C160" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D160" t="n">
-        <v>17381</v>
+        <v>6627002</v>
       </c>
       <c r="E160" t="n">
-        <v>0.13</v>
+        <v>49.84</v>
       </c>
       <c r="F160" t="n">
-        <v>0.13</v>
+        <v>49.84</v>
       </c>
       <c r="G160" t="n">
-        <v>99.83</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B161" t="n">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="C161" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D161" t="n">
-        <v>23055</v>
+        <v>349411</v>
       </c>
       <c r="E161" t="n">
-        <v>0.17</v>
+        <v>2.63</v>
       </c>
       <c r="F161" t="n">
-        <v>0.17</v>
+        <v>2.63</v>
       </c>
       <c r="G161" t="n">
-        <v>100</v>
+        <v>99.83</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B162" s="2"/>
-      <c r="C162" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="D162" s="2" t="n">
-        <v>0</v>
+        <v>23033</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F162" s="2"/>
-      <c r="G162" s="2"/>
+        <v>0.17</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B163" t="n">
         <v>1</v>
       </c>
       <c r="C163" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D163" t="n">
-        <v>3798414</v>
+        <v>3716809</v>
       </c>
       <c r="E163" t="n">
-        <v>28.57</v>
+        <v>27.95</v>
       </c>
       <c r="F163" t="n">
-        <v>28.57</v>
+        <v>27.95</v>
       </c>
       <c r="G163" t="n">
-        <v>28.57</v>
+        <v>27.95</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B164" t="n">
         <v>2</v>
       </c>
       <c r="C164" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D164" t="n">
-        <v>4536571</v>
+        <v>4376382</v>
       </c>
       <c r="E164" t="n">
-        <v>34.12</v>
+        <v>32.91</v>
       </c>
       <c r="F164" t="n">
-        <v>34.12</v>
+        <v>32.91</v>
       </c>
       <c r="G164" t="n">
-        <v>62.69</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B165" t="n">
         <v>3</v>
       </c>
       <c r="C165" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D165" t="n">
-        <v>4954688</v>
+        <v>5179323</v>
       </c>
       <c r="E165" t="n">
-        <v>37.26</v>
+        <v>38.95</v>
       </c>
       <c r="F165" t="n">
-        <v>37.26</v>
+        <v>38.95</v>
       </c>
       <c r="G165" t="n">
-        <v>99.95</v>
+        <v>99.82</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B166" t="n">
         <v>85</v>
@@ -4293,21 +4373,21 @@
         <v>22</v>
       </c>
       <c r="D166" t="n">
-        <v>6216</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>100</v>
+        <v>99.82</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B167" t="n">
         <v>88</v>
@@ -4316,468 +4396,178 @@
         <v>23</v>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>9270</v>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>0.07</v>
       </c>
       <c r="G167" t="n">
+        <v>99.89</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>14275</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G168" s="2" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>40</v>
-      </c>
-      <c r="B168" t="n">
-        <v>99</v>
-      </c>
-      <c r="C168" t="s">
-        <v>24</v>
-      </c>
-      <c r="D168" t="n">
-        <v>169</v>
-      </c>
-      <c r="E168" t="n">
-        <v>0</v>
-      </c>
-      <c r="F168" t="n">
-        <v>0</v>
-      </c>
-      <c r="G168" t="n">
-        <v>100</v>
-      </c>
-    </row>
     <row r="169">
-      <c r="A169" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B169" s="2"/>
-      <c r="C169" s="2"/>
-      <c r="D169" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E169" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F169" s="2"/>
-      <c r="G169" s="2"/>
+      <c r="A169" t="s">
+        <v>51</v>
+      </c>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" t="s">
+        <v>52</v>
+      </c>
+      <c r="D169" t="n">
+        <v>3438194</v>
+      </c>
+      <c r="E169" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="F169" t="n">
+        <v>25.86</v>
+      </c>
+      <c r="G169" t="n">
+        <v>25.86</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C170" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D170" t="n">
-        <v>6295807</v>
+        <v>4260841</v>
       </c>
       <c r="E170" t="n">
-        <v>47.35</v>
+        <v>32.05</v>
       </c>
       <c r="F170" t="n">
-        <v>47.35</v>
+        <v>32.05</v>
       </c>
       <c r="G170" t="n">
-        <v>47.35</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B171" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C171" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D171" t="n">
-        <v>6627002</v>
+        <v>5212156</v>
       </c>
       <c r="E171" t="n">
-        <v>49.84</v>
+        <v>39.2</v>
       </c>
       <c r="F171" t="n">
-        <v>49.84</v>
+        <v>39.2</v>
       </c>
       <c r="G171" t="n">
-        <v>97.2</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B172" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C172" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D172" t="n">
-        <v>349411</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>99.83</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B173" t="n">
+        <v>88</v>
+      </c>
+      <c r="C173" t="s">
+        <v>23</v>
+      </c>
+      <c r="D173" t="n">
+        <v>371956</v>
+      </c>
+      <c r="E173" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G173" t="n">
+        <v>99.9</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>51</v>
+      </c>
+      <c r="B174" t="n">
         <v>99</v>
       </c>
-      <c r="C173" t="s">
+      <c r="C174" t="s">
         <v>24</v>
       </c>
-      <c r="D173" t="n">
-        <v>23033</v>
-      </c>
-      <c r="E173" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G173" t="n">
+      <c r="D174" t="n">
+        <v>12911</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G174" t="n">
         <v>100</v>
       </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B174" s="2"/>
-      <c r="C174" s="2"/>
-      <c r="D174" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E174" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F174" s="2"/>
-      <c r="G174" s="2"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>47</v>
-      </c>
-      <c r="B175" t="n">
-        <v>1</v>
-      </c>
-      <c r="C175" t="s">
-        <v>48</v>
-      </c>
-      <c r="D175" t="n">
-        <v>3716809</v>
-      </c>
-      <c r="E175" t="n">
-        <v>27.95</v>
-      </c>
-      <c r="F175" t="n">
-        <v>27.95</v>
-      </c>
-      <c r="G175" t="n">
-        <v>27.95</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>47</v>
-      </c>
-      <c r="B176" t="n">
-        <v>2</v>
-      </c>
-      <c r="C176" t="s">
-        <v>49</v>
-      </c>
-      <c r="D176" t="n">
-        <v>4376382</v>
-      </c>
-      <c r="E176" t="n">
-        <v>32.91</v>
-      </c>
-      <c r="F176" t="n">
-        <v>32.91</v>
-      </c>
-      <c r="G176" t="n">
-        <v>60.87</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>47</v>
-      </c>
-      <c r="B177" t="n">
-        <v>3</v>
-      </c>
-      <c r="C177" t="s">
-        <v>50</v>
-      </c>
-      <c r="D177" t="n">
-        <v>5179323</v>
-      </c>
-      <c r="E177" t="n">
-        <v>38.95</v>
-      </c>
-      <c r="F177" t="n">
-        <v>38.95</v>
-      </c>
-      <c r="G177" t="n">
-        <v>99.82</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>47</v>
-      </c>
-      <c r="B178" t="n">
-        <v>85</v>
-      </c>
-      <c r="C178" t="s">
-        <v>22</v>
-      </c>
-      <c r="D178" t="n">
-        <v>0</v>
-      </c>
-      <c r="E178" t="n">
-        <v>0</v>
-      </c>
-      <c r="F178" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" t="n">
-        <v>99.82</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>47</v>
-      </c>
-      <c r="B179" t="n">
-        <v>88</v>
-      </c>
-      <c r="C179" t="s">
-        <v>23</v>
-      </c>
-      <c r="D179" t="n">
-        <v>9270</v>
-      </c>
-      <c r="E179" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="F179" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="G179" t="n">
-        <v>99.89</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>47</v>
-      </c>
-      <c r="B180" t="n">
-        <v>99</v>
-      </c>
-      <c r="C180" t="s">
-        <v>24</v>
-      </c>
-      <c r="D180" t="n">
-        <v>14275</v>
-      </c>
-      <c r="E180" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F180" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G180" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B181" s="2"/>
-      <c r="C181" s="2"/>
-      <c r="D181" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E181" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" s="2"/>
-      <c r="G181" s="2"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>51</v>
-      </c>
-      <c r="B182" t="n">
-        <v>1</v>
-      </c>
-      <c r="C182" t="s">
-        <v>52</v>
-      </c>
-      <c r="D182" t="n">
-        <v>3438194</v>
-      </c>
-      <c r="E182" t="n">
-        <v>25.86</v>
-      </c>
-      <c r="F182" t="n">
-        <v>25.86</v>
-      </c>
-      <c r="G182" t="n">
-        <v>25.86</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>51</v>
-      </c>
-      <c r="B183" t="n">
-        <v>2</v>
-      </c>
-      <c r="C183" t="s">
-        <v>53</v>
-      </c>
-      <c r="D183" t="n">
-        <v>4260841</v>
-      </c>
-      <c r="E183" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="F183" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="G183" t="n">
-        <v>57.9</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>51</v>
-      </c>
-      <c r="B184" t="n">
-        <v>3</v>
-      </c>
-      <c r="C184" t="s">
-        <v>54</v>
-      </c>
-      <c r="D184" t="n">
-        <v>5212156</v>
-      </c>
-      <c r="E184" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="F184" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="G184" t="n">
-        <v>97.11</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>51</v>
-      </c>
-      <c r="B185" t="n">
-        <v>85</v>
-      </c>
-      <c r="C185" t="s">
-        <v>22</v>
-      </c>
-      <c r="D185" t="n">
-        <v>0</v>
-      </c>
-      <c r="E185" t="n">
-        <v>0</v>
-      </c>
-      <c r="F185" t="n">
-        <v>0</v>
-      </c>
-      <c r="G185" t="n">
-        <v>97.11</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>51</v>
-      </c>
-      <c r="B186" t="n">
-        <v>88</v>
-      </c>
-      <c r="C186" t="s">
-        <v>23</v>
-      </c>
-      <c r="D186" t="n">
-        <v>371956</v>
-      </c>
-      <c r="E186" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F186" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G186" t="n">
-        <v>99.9</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>51</v>
-      </c>
-      <c r="B187" t="n">
-        <v>99</v>
-      </c>
-      <c r="C187" t="s">
-        <v>24</v>
-      </c>
-      <c r="D187" t="n">
-        <v>12911</v>
-      </c>
-      <c r="E187" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F187" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G187" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>51</v>
-      </c>
-      <c r="B188"/>
-      <c r="C188"/>
-      <c r="D188" t="n">
-        <v>0</v>
-      </c>
-      <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188"/>
-      <c r="G188"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>

--- a/output/tables/2025/tabla2_variables_fuente.xlsx
+++ b/output/tables/2025/tabla2_variables_fuente.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">comgen_com_pct</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_ep_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_ep_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja inseguridad en espacio publico</t>
@@ -90,7 +90,7 @@
     <t xml:space="preserve">No responde</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_barrio_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_barrio_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja inseguridad en el barrio</t>
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Alta inseguridad en el barrio</t>
   </si>
   <si>
-    <t xml:space="preserve">emper_casa_pct_rec_tercil</t>
+    <t xml:space="preserve">emper_casa_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja inseguridad en la casa</t>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">No sabe/No responde de qué delito será victima</t>
   </si>
   <si>
-    <t xml:space="preserve">comper_pct_rec_tercil</t>
+    <t xml:space="preserve">comper_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Bajas prácticas de evitación</t>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Gasta en medidas de seguridad</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_per_pct_rec_tercil</t>
+    <t xml:space="preserve">comgen_per_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja disposición de medidas vivienda</t>
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Alta disposición de medidas vivienda</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_com_pct_rec_tercil</t>
+    <t xml:space="preserve">comgen_com_pct_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Baja adopción de medidas comunitarias</t>
@@ -558,7 +558,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="27.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="55.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="8.71" hidden="0" customWidth="1"/>

--- a/output/tables/2025/tabla2_variables_fuente.xlsx
+++ b/output/tables/2025/tabla2_variables_fuente.xlsx
@@ -72,13 +72,13 @@
     <t xml:space="preserve">emper_ep_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Baja inseguridad en espacio publico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media inseguridad en espacio publico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta inseguridad en espacio publico</t>
+    <t xml:space="preserve">Sin inseguridad en espacio público</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en hasta la mitad de los lugares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en más de la mitad de los lugares</t>
   </si>
   <si>
     <t xml:space="preserve">No aplica</t>
@@ -93,25 +93,25 @@
     <t xml:space="preserve">emper_barrio_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Baja inseguridad en el barrio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media inseguridad en el barrio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta inseguridad en el barrio</t>
+    <t xml:space="preserve">Sin inseguridad en el barrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en el barrio, de día o de noche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en el barrio, de día y de noche</t>
   </si>
   <si>
     <t xml:space="preserve">emper_casa_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Baja inseguridad en la casa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media inseguridad en la casa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta inseguridad en la casa</t>
+    <t xml:space="preserve">Sin inseguridad en la casa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en la casa, de día o de noche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inseguridad en la casa, de día y de noche</t>
   </si>
   <si>
     <t xml:space="preserve">perper_delito</t>
@@ -138,13 +138,13 @@
     <t xml:space="preserve">comper_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Bajas prácticas de evitación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medias prácticas de evitación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Altas prácticas de evitación</t>
+    <t xml:space="preserve">No modificó prácticas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modificó hasta la mitad de las prácticas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modificó más de la mitad de las prácticas</t>
   </si>
   <si>
     <t xml:space="preserve">comper_gasto</t>
@@ -159,25 +159,25 @@
     <t xml:space="preserve">comgen_per_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Baja disposición de medidas vivienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media disposición de medidas vivienda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta disposición de medidas vivienda</t>
+    <t xml:space="preserve">Sin medidas en la vivienda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una o dos medidas en la vivienda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tres o más medidas en la vivienda</t>
   </si>
   <si>
     <t xml:space="preserve">comgen_com_pct_cat</t>
   </si>
   <si>
-    <t xml:space="preserve">Baja adopción de medidas comunitarias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media adopción de medidas comunitarias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alta adopción de medidas comunitarias</t>
+    <t xml:space="preserve">Sin medidas en el barrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una medida en el barrio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dos o más medidas en el barrio</t>
   </si>
 </sst>
 </file>
@@ -3522,16 +3522,16 @@
         <v>19</v>
       </c>
       <c r="D129" t="n">
-        <v>3735069</v>
+        <v>2252060</v>
       </c>
       <c r="E129" t="n">
-        <v>28.09</v>
+        <v>16.94</v>
       </c>
       <c r="F129" t="n">
-        <v>28.09</v>
+        <v>16.94</v>
       </c>
       <c r="G129" t="n">
-        <v>28.09</v>
+        <v>16.94</v>
       </c>
     </row>
     <row r="130">
@@ -3545,16 +3545,16 @@
         <v>20</v>
       </c>
       <c r="D130" t="n">
-        <v>4754124</v>
+        <v>5900237</v>
       </c>
       <c r="E130" t="n">
-        <v>35.76</v>
+        <v>44.38</v>
       </c>
       <c r="F130" t="n">
-        <v>35.76</v>
+        <v>44.38</v>
       </c>
       <c r="G130" t="n">
-        <v>63.85</v>
+        <v>61.31</v>
       </c>
     </row>
     <row r="131">
@@ -3568,13 +3568,13 @@
         <v>21</v>
       </c>
       <c r="D131" t="n">
-        <v>4781865</v>
+        <v>5118761</v>
       </c>
       <c r="E131" t="n">
-        <v>35.96</v>
+        <v>38.5</v>
       </c>
       <c r="F131" t="n">
-        <v>35.96</v>
+        <v>38.5</v>
       </c>
       <c r="G131" t="n">
         <v>99.81</v>
@@ -3660,16 +3660,16 @@
         <v>26</v>
       </c>
       <c r="D135" t="n">
-        <v>3724967</v>
+        <v>4138480</v>
       </c>
       <c r="E135" t="n">
-        <v>28.02</v>
+        <v>31.13</v>
       </c>
       <c r="F135" t="n">
-        <v>28.02</v>
+        <v>31.13</v>
       </c>
       <c r="G135" t="n">
-        <v>28.02</v>
+        <v>31.13</v>
       </c>
     </row>
     <row r="136">
@@ -3683,16 +3683,16 @@
         <v>27</v>
       </c>
       <c r="D136" t="n">
-        <v>4365275</v>
+        <v>5574634</v>
       </c>
       <c r="E136" t="n">
-        <v>32.83</v>
+        <v>41.93</v>
       </c>
       <c r="F136" t="n">
-        <v>32.83</v>
+        <v>41.93</v>
       </c>
       <c r="G136" t="n">
-        <v>60.85</v>
+        <v>73.05</v>
       </c>
     </row>
     <row r="137">
@@ -3706,13 +3706,13 @@
         <v>28</v>
       </c>
       <c r="D137" t="n">
-        <v>5016942</v>
+        <v>3394070</v>
       </c>
       <c r="E137" t="n">
-        <v>37.73</v>
+        <v>25.53</v>
       </c>
       <c r="F137" t="n">
-        <v>37.73</v>
+        <v>25.53</v>
       </c>
       <c r="G137" t="n">
         <v>98.58</v>
@@ -3798,16 +3798,16 @@
         <v>30</v>
       </c>
       <c r="D141" t="n">
-        <v>4582770</v>
+        <v>10296748</v>
       </c>
       <c r="E141" t="n">
-        <v>34.47</v>
+        <v>77.44</v>
       </c>
       <c r="F141" t="n">
-        <v>34.47</v>
+        <v>77.44</v>
       </c>
       <c r="G141" t="n">
-        <v>34.47</v>
+        <v>77.44</v>
       </c>
     </row>
     <row r="142">
@@ -3821,16 +3821,16 @@
         <v>31</v>
       </c>
       <c r="D142" t="n">
-        <v>4490784</v>
+        <v>1763276</v>
       </c>
       <c r="E142" t="n">
-        <v>33.78</v>
+        <v>13.26</v>
       </c>
       <c r="F142" t="n">
-        <v>33.78</v>
+        <v>13.26</v>
       </c>
       <c r="G142" t="n">
-        <v>68.24</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="143">
@@ -3844,13 +3844,13 @@
         <v>32</v>
       </c>
       <c r="D143" t="n">
-        <v>4197523</v>
+        <v>1211052</v>
       </c>
       <c r="E143" t="n">
-        <v>31.57</v>
+        <v>9.11</v>
       </c>
       <c r="F143" t="n">
-        <v>31.57</v>
+        <v>9.11</v>
       </c>
       <c r="G143" t="n">
         <v>99.81</v>
@@ -4074,16 +4074,16 @@
         <v>41</v>
       </c>
       <c r="D153" t="n">
-        <v>3798414</v>
+        <v>1824589</v>
       </c>
       <c r="E153" t="n">
-        <v>28.57</v>
+        <v>13.72</v>
       </c>
       <c r="F153" t="n">
-        <v>28.57</v>
+        <v>13.72</v>
       </c>
       <c r="G153" t="n">
-        <v>28.57</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="154">
@@ -4097,16 +4097,16 @@
         <v>42</v>
       </c>
       <c r="D154" t="n">
-        <v>4536571</v>
+        <v>6465234</v>
       </c>
       <c r="E154" t="n">
-        <v>34.12</v>
+        <v>48.63</v>
       </c>
       <c r="F154" t="n">
-        <v>34.12</v>
+        <v>48.63</v>
       </c>
       <c r="G154" t="n">
-        <v>62.69</v>
+        <v>62.35</v>
       </c>
     </row>
     <row r="155">
@@ -4120,13 +4120,13 @@
         <v>43</v>
       </c>
       <c r="D155" t="n">
-        <v>4954688</v>
+        <v>4999850</v>
       </c>
       <c r="E155" t="n">
-        <v>37.26</v>
+        <v>37.6</v>
       </c>
       <c r="F155" t="n">
-        <v>37.26</v>
+        <v>37.6</v>
       </c>
       <c r="G155" t="n">
         <v>99.95</v>
@@ -4304,16 +4304,16 @@
         <v>48</v>
       </c>
       <c r="D163" t="n">
-        <v>3716809</v>
+        <v>1088781</v>
       </c>
       <c r="E163" t="n">
-        <v>27.95</v>
+        <v>8.19</v>
       </c>
       <c r="F163" t="n">
-        <v>27.95</v>
+        <v>8.19</v>
       </c>
       <c r="G163" t="n">
-        <v>27.95</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="164">
@@ -4327,16 +4327,16 @@
         <v>49</v>
       </c>
       <c r="D164" t="n">
-        <v>4376382</v>
+        <v>6660299</v>
       </c>
       <c r="E164" t="n">
-        <v>32.91</v>
+        <v>50.09</v>
       </c>
       <c r="F164" t="n">
-        <v>32.91</v>
+        <v>50.09</v>
       </c>
       <c r="G164" t="n">
-        <v>60.87</v>
+        <v>58.28</v>
       </c>
     </row>
     <row r="165">
@@ -4350,13 +4350,13 @@
         <v>50</v>
       </c>
       <c r="D165" t="n">
-        <v>5179323</v>
+        <v>5523433</v>
       </c>
       <c r="E165" t="n">
-        <v>38.95</v>
+        <v>41.54</v>
       </c>
       <c r="F165" t="n">
-        <v>38.95</v>
+        <v>41.54</v>
       </c>
       <c r="G165" t="n">
         <v>99.82</v>
@@ -4442,16 +4442,16 @@
         <v>52</v>
       </c>
       <c r="D169" t="n">
-        <v>3438194</v>
+        <v>3267358</v>
       </c>
       <c r="E169" t="n">
-        <v>25.86</v>
+        <v>24.57</v>
       </c>
       <c r="F169" t="n">
-        <v>25.86</v>
+        <v>24.57</v>
       </c>
       <c r="G169" t="n">
-        <v>25.86</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="170">
@@ -4465,16 +4465,16 @@
         <v>53</v>
       </c>
       <c r="D170" t="n">
-        <v>4260841</v>
+        <v>3603876</v>
       </c>
       <c r="E170" t="n">
-        <v>32.05</v>
+        <v>27.1</v>
       </c>
       <c r="F170" t="n">
-        <v>32.05</v>
+        <v>27.1</v>
       </c>
       <c r="G170" t="n">
-        <v>57.9</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="171">
@@ -4488,13 +4488,13 @@
         <v>54</v>
       </c>
       <c r="D171" t="n">
-        <v>5212156</v>
+        <v>6039957</v>
       </c>
       <c r="E171" t="n">
-        <v>39.2</v>
+        <v>45.43</v>
       </c>
       <c r="F171" t="n">
-        <v>39.2</v>
+        <v>45.43</v>
       </c>
       <c r="G171" t="n">
         <v>97.11</v>

--- a/output/tables/2025/tabla2_variables_fuente.xlsx
+++ b/output/tables/2025/tabla2_variables_fuente.xlsx
@@ -6,26 +6,13 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="AVISO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variables_fuente" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="variables_fuente" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
-  <si>
-    <t xml:space="preserve">aviso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">motivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROVISIONAL - no citar como número final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2 abierta (PLAN.md): la categorización en terciles (ntile) de los índices _pct puede cambiar. Los índices _pct continuos no dependen de D2.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -530,33 +517,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="5.71" hidden="0" customWidth="1"/>
@@ -569,36 +529,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>2252229</v>
@@ -615,13 +575,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" t="n">
         <v>9.09</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>189986</v>
@@ -638,13 +598,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>240524</v>
@@ -661,13 +621,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n">
         <v>11.11</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>228697</v>
@@ -684,13 +644,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
         <v>12.5</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>234180</v>
@@ -707,13 +667,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" t="n">
         <v>14.29</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>253819</v>
@@ -730,13 +690,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
         <v>16.67</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>204454</v>
@@ -753,13 +713,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B9" t="n">
         <v>18.18</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>192674</v>
@@ -776,13 +736,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B10" t="n">
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>368947</v>
@@ -799,13 +759,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
         <v>22.22</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>215346</v>
@@ -822,13 +782,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B12" t="n">
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>333553</v>
@@ -845,13 +805,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B13" t="n">
         <v>27.27</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>183444</v>
@@ -868,13 +828,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B14" t="n">
         <v>28.57</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>225584</v>
@@ -891,13 +851,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B15" t="n">
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>238492</v>
@@ -914,13 +874,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B16" t="n">
         <v>33.33</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>491627</v>
@@ -937,13 +897,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B17" t="n">
         <v>36.36</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>226347</v>
@@ -960,13 +920,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B18" t="n">
         <v>37.5</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>215680</v>
@@ -983,13 +943,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B19" t="n">
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>380926</v>
@@ -1006,13 +966,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B20" t="n">
         <v>42.86</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>222450</v>
@@ -1029,13 +989,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B21" t="n">
         <v>44.44</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
         <v>223503</v>
@@ -1052,13 +1012,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B22" t="n">
         <v>45.45</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
         <v>230028</v>
@@ -1075,13 +1035,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B23" t="n">
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
         <v>799975</v>
@@ -1098,13 +1058,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B24" t="n">
         <v>54.55</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
         <v>231453</v>
@@ -1121,13 +1081,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B25" t="n">
         <v>55.56</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
         <v>226334</v>
@@ -1144,13 +1104,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B26" t="n">
         <v>57.14</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
         <v>204906</v>
@@ -1167,13 +1127,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B27" t="n">
         <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
         <v>360984</v>
@@ -1190,13 +1150,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B28" t="n">
         <v>62.5</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
         <v>211198</v>
@@ -1213,13 +1173,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B29" t="n">
         <v>63.64</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
         <v>214916</v>
@@ -1236,13 +1196,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B30" t="n">
         <v>66.67</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
         <v>445512</v>
@@ -1259,13 +1219,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B31" t="n">
         <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
         <v>209985</v>
@@ -1282,13 +1242,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
         <v>71.43</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D32" t="n">
         <v>171704</v>
@@ -1305,13 +1265,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B33" t="n">
         <v>72.73</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D33" t="n">
         <v>208040</v>
@@ -1328,13 +1288,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B34" t="n">
         <v>75</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
         <v>285372</v>
@@ -1351,13 +1311,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B35" t="n">
         <v>77.78</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
         <v>165175</v>
@@ -1374,13 +1334,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B36" t="n">
         <v>80</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D36" t="n">
         <v>295424</v>
@@ -1397,13 +1357,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B37" t="n">
         <v>81.82</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
         <v>167006</v>
@@ -1420,13 +1380,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B38" t="n">
         <v>83.33</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D38" t="n">
         <v>142050</v>
@@ -1443,13 +1403,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B39" t="n">
         <v>85.71</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D39" t="n">
         <v>131952</v>
@@ -1466,13 +1426,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B40" t="n">
         <v>87.5</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D40" t="n">
         <v>130625</v>
@@ -1489,13 +1449,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B41" t="n">
         <v>88.89</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D41" t="n">
         <v>123268</v>
@@ -1512,13 +1472,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B42" t="n">
         <v>90</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D42" t="n">
         <v>135809</v>
@@ -1535,13 +1495,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B43" t="n">
         <v>90.91</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D43" t="n">
         <v>138125</v>
@@ -1558,13 +1518,13 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>100</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>918924</v>
@@ -1581,13 +1541,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D45" t="n">
         <v>4140827</v>
@@ -1604,13 +1564,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B46" t="n">
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D46" t="n">
         <v>5574634</v>
@@ -1627,13 +1587,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>100</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>3394070</v>
@@ -1650,13 +1610,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D48" t="n">
         <v>10297783</v>
@@ -1673,13 +1633,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B49" t="n">
         <v>50</v>
       </c>
       <c r="C49" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
         <v>1763276</v>
@@ -1696,13 +1656,13 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>100</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>1211052</v>
@@ -1719,13 +1679,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D51" t="n">
         <v>1824758</v>
@@ -1742,13 +1702,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B52" t="n">
         <v>7.69</v>
       </c>
       <c r="C52" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D52" t="n">
         <v>267128</v>
@@ -1765,13 +1725,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B53" t="n">
         <v>8.33</v>
       </c>
       <c r="C53" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
         <v>301494</v>
@@ -1788,13 +1748,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B54" t="n">
         <v>9.09</v>
       </c>
       <c r="C54" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D54" t="n">
         <v>243848</v>
@@ -1811,13 +1771,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B55" t="n">
         <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D55" t="n">
         <v>214615</v>
@@ -1834,13 +1794,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B56" t="n">
         <v>11.11</v>
       </c>
       <c r="C56" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D56" t="n">
         <v>140033</v>
@@ -1857,13 +1817,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B57" t="n">
         <v>12.5</v>
       </c>
       <c r="C57" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D57" t="n">
         <v>88207</v>
@@ -1880,13 +1840,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B58" t="n">
         <v>14.29</v>
       </c>
       <c r="C58" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D58" t="n">
         <v>50648</v>
@@ -1903,13 +1863,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B59" t="n">
         <v>15.38</v>
       </c>
       <c r="C59" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D59" t="n">
         <v>266899</v>
@@ -1926,13 +1886,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B60" t="n">
         <v>16.67</v>
       </c>
       <c r="C60" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D60" t="n">
         <v>325959</v>
@@ -1949,13 +1909,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B61" t="n">
         <v>18.18</v>
       </c>
       <c r="C61" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D61" t="n">
         <v>232941</v>
@@ -1972,13 +1932,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B62" t="n">
         <v>20</v>
       </c>
       <c r="C62" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
         <v>199499</v>
@@ -1995,13 +1955,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B63" t="n">
         <v>22.22</v>
       </c>
       <c r="C63" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D63" t="n">
         <v>131534</v>
@@ -2018,13 +1978,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B64" t="n">
         <v>23.08</v>
       </c>
       <c r="C64" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D64" t="n">
         <v>265504</v>
@@ -2041,13 +2001,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B65" t="n">
         <v>25</v>
       </c>
       <c r="C65" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D65" t="n">
         <v>371449</v>
@@ -2064,13 +2024,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B66" t="n">
         <v>27.27</v>
       </c>
       <c r="C66" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D66" t="n">
         <v>226839</v>
@@ -2087,13 +2047,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B67" t="n">
         <v>28.57</v>
       </c>
       <c r="C67" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D67" t="n">
         <v>44530</v>
@@ -2110,13 +2070,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B68" t="n">
         <v>30</v>
       </c>
       <c r="C68" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D68" t="n">
         <v>197133</v>
@@ -2133,13 +2093,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B69" t="n">
         <v>30.77</v>
       </c>
       <c r="C69" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D69" t="n">
         <v>272739</v>
@@ -2156,13 +2116,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B70" t="n">
         <v>33.33</v>
       </c>
       <c r="C70" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D70" t="n">
         <v>404592</v>
@@ -2179,13 +2139,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B71" t="n">
         <v>36.36</v>
       </c>
       <c r="C71" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D71" t="n">
         <v>215735</v>
@@ -2202,13 +2162,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B72" t="n">
         <v>37.5</v>
       </c>
       <c r="C72" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D72" t="n">
         <v>65768</v>
@@ -2225,13 +2185,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B73" t="n">
         <v>38.46</v>
       </c>
       <c r="C73" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D73" t="n">
         <v>268833</v>
@@ -2248,13 +2208,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B74" t="n">
         <v>40</v>
       </c>
       <c r="C74" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D74" t="n">
         <v>197838</v>
@@ -2271,13 +2231,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B75" t="n">
         <v>41.67</v>
       </c>
       <c r="C75" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D75" t="n">
         <v>296644</v>
@@ -2294,13 +2254,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B76" t="n">
         <v>42.86</v>
       </c>
       <c r="C76" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D76" t="n">
         <v>34752</v>
@@ -2317,13 +2277,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B77" t="n">
         <v>44.44</v>
       </c>
       <c r="C77" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D77" t="n">
         <v>101606</v>
@@ -2340,13 +2300,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B78" t="n">
         <v>45.45</v>
       </c>
       <c r="C78" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D78" t="n">
         <v>220048</v>
@@ -2363,13 +2323,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B79" t="n">
         <v>46.15</v>
       </c>
       <c r="C79" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D79" t="n">
         <v>255399</v>
@@ -2386,13 +2346,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B80" t="n">
         <v>50</v>
       </c>
       <c r="C80" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D80" t="n">
         <v>563017</v>
@@ -2409,13 +2369,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B81" t="n">
         <v>53.85</v>
       </c>
       <c r="C81" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D81" t="n">
         <v>290589</v>
@@ -2432,13 +2392,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B82" t="n">
         <v>54.55</v>
       </c>
       <c r="C82" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D82" t="n">
         <v>230077</v>
@@ -2455,13 +2415,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B83" t="n">
         <v>55.56</v>
       </c>
       <c r="C83" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D83" t="n">
         <v>107622</v>
@@ -2478,13 +2438,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B84" t="n">
         <v>57.14</v>
       </c>
       <c r="C84" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D84" t="n">
         <v>34854</v>
@@ -2501,13 +2461,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B85" t="n">
         <v>58.33</v>
       </c>
       <c r="C85" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D85" t="n">
         <v>308641</v>
@@ -2524,13 +2484,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B86" t="n">
         <v>60</v>
       </c>
       <c r="C86" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D86" t="n">
         <v>182526</v>
@@ -2547,13 +2507,13 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B87" t="n">
         <v>61.54</v>
       </c>
       <c r="C87" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D87" t="n">
         <v>304420</v>
@@ -2570,13 +2530,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B88" t="n">
         <v>62.5</v>
       </c>
       <c r="C88" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D88" t="n">
         <v>53695</v>
@@ -2593,13 +2553,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B89" t="n">
         <v>63.64</v>
       </c>
       <c r="C89" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D89" t="n">
         <v>232015</v>
@@ -2616,13 +2576,13 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B90" t="n">
         <v>66.67</v>
       </c>
       <c r="C90" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D90" t="n">
         <v>415027</v>
@@ -2639,13 +2599,13 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B91" t="n">
         <v>69.23</v>
       </c>
       <c r="C91" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D91" t="n">
         <v>278666</v>
@@ -2662,13 +2622,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B92" t="n">
         <v>70</v>
       </c>
       <c r="C92" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D92" t="n">
         <v>167594</v>
@@ -2685,13 +2645,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B93" t="n">
         <v>71.43</v>
       </c>
       <c r="C93" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D93" t="n">
         <v>26189</v>
@@ -2708,13 +2668,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B94" t="n">
         <v>72.73</v>
       </c>
       <c r="C94" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D94" t="n">
         <v>191508</v>
@@ -2731,13 +2691,13 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B95" t="n">
         <v>75</v>
       </c>
       <c r="C95" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D95" t="n">
         <v>293168</v>
@@ -2754,13 +2714,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B96" t="n">
         <v>76.92</v>
       </c>
       <c r="C96" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D96" t="n">
         <v>246761</v>
@@ -2777,13 +2737,13 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B97" t="n">
         <v>77.78</v>
       </c>
       <c r="C97" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D97" t="n">
         <v>93784</v>
@@ -2800,13 +2760,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B98" t="n">
         <v>80</v>
       </c>
       <c r="C98" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D98" t="n">
         <v>138238</v>
@@ -2823,13 +2783,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B99" t="n">
         <v>81.82</v>
       </c>
       <c r="C99" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D99" t="n">
         <v>134103</v>
@@ -2846,13 +2806,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B100" t="n">
         <v>83.33</v>
       </c>
       <c r="C100" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D100" t="n">
         <v>182802</v>
@@ -2869,13 +2829,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B101" t="n">
         <v>84.62</v>
       </c>
       <c r="C101" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D101" t="n">
         <v>213226</v>
@@ -2892,13 +2852,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B102" t="n">
         <v>85.71</v>
       </c>
       <c r="C102" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D102" t="n">
         <v>18694</v>
@@ -2915,13 +2875,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B103" t="n">
         <v>87.5</v>
       </c>
       <c r="C103" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D103" t="n">
         <v>31560</v>
@@ -2938,13 +2898,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B104" t="n">
         <v>88.89</v>
       </c>
       <c r="C104" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D104" t="n">
         <v>50099</v>
@@ -2961,13 +2921,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B105" t="n">
         <v>90</v>
       </c>
       <c r="C105" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D105" t="n">
         <v>93401</v>
@@ -2984,13 +2944,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B106" t="n">
         <v>90.91</v>
       </c>
       <c r="C106" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D106" t="n">
         <v>95380</v>
@@ -3007,13 +2967,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B107" t="n">
         <v>91.67</v>
       </c>
       <c r="C107" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D107" t="n">
         <v>119820</v>
@@ -3030,13 +2990,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B108" t="n">
         <v>92.31</v>
       </c>
       <c r="C108" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D108" t="n">
         <v>172469</v>
@@ -3053,13 +3013,13 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>100</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>292921</v>
@@ -3076,13 +3036,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B110" t="n">
         <v>0</v>
       </c>
       <c r="C110" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D110" t="n">
         <v>1088781</v>
@@ -3099,13 +3059,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B111" t="n">
         <v>11.11</v>
       </c>
       <c r="C111" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D111" t="n">
         <v>3103365</v>
@@ -3122,13 +3082,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B112" t="n">
         <v>22.22</v>
       </c>
       <c r="C112" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D112" t="n">
         <v>3556934</v>
@@ -3145,13 +3105,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B113" t="n">
         <v>33.33</v>
       </c>
       <c r="C113" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D113" t="n">
         <v>2631062</v>
@@ -3168,13 +3128,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B114" t="n">
         <v>44.44</v>
       </c>
       <c r="C114" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D114" t="n">
         <v>1528379</v>
@@ -3191,13 +3151,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B115" t="n">
         <v>55.56</v>
       </c>
       <c r="C115" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D115" t="n">
         <v>782192</v>
@@ -3214,13 +3174,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B116" t="n">
         <v>66.67</v>
       </c>
       <c r="C116" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D116" t="n">
         <v>381157</v>
@@ -3237,13 +3197,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B117" t="n">
         <v>77.78</v>
       </c>
       <c r="C117" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D117" t="n">
         <v>162624</v>
@@ -3260,13 +3220,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B118" t="n">
         <v>88.89</v>
       </c>
       <c r="C118" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D118" t="n">
         <v>36088</v>
@@ -3283,13 +3243,13 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B119" s="2" t="n">
         <v>100</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>1931</v>
@@ -3306,13 +3266,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B120" t="n">
         <v>0</v>
       </c>
       <c r="C120" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D120" t="n">
         <v>3267358</v>
@@ -3329,13 +3289,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B121" t="n">
         <v>12.5</v>
       </c>
       <c r="C121" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D121" t="n">
         <v>3603876</v>
@@ -3352,13 +3312,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B122" t="n">
         <v>25</v>
       </c>
       <c r="C122" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D122" t="n">
         <v>2923576</v>
@@ -3375,13 +3335,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B123" t="n">
         <v>37.5</v>
       </c>
       <c r="C123" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D123" t="n">
         <v>1706426</v>
@@ -3398,13 +3358,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B124" t="n">
         <v>50</v>
       </c>
       <c r="C124" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D124" t="n">
         <v>805341</v>
@@ -3421,13 +3381,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B125" t="n">
         <v>62.5</v>
       </c>
       <c r="C125" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D125" t="n">
         <v>418863</v>
@@ -3444,13 +3404,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B126" t="n">
         <v>75</v>
       </c>
       <c r="C126" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D126" t="n">
         <v>152816</v>
@@ -3467,13 +3427,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B127" t="n">
         <v>87.5</v>
       </c>
       <c r="C127" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D127" t="n">
         <v>29418</v>
@@ -3490,13 +3450,13 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>100</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>3517</v>
@@ -3513,13 +3473,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B129" t="n">
         <v>1</v>
       </c>
       <c r="C129" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D129" t="n">
         <v>2252060</v>
@@ -3536,13 +3496,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B130" t="n">
         <v>2</v>
       </c>
       <c r="C130" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D130" t="n">
         <v>5900237</v>
@@ -3559,13 +3519,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B131" t="n">
         <v>3</v>
       </c>
       <c r="C131" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D131" t="n">
         <v>5118761</v>
@@ -3582,13 +3542,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B132" t="n">
         <v>85</v>
       </c>
       <c r="C132" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D132" t="n">
         <v>24831</v>
@@ -3605,13 +3565,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B133" t="n">
         <v>88</v>
       </c>
       <c r="C133" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -3628,13 +3588,13 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B134" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>169</v>
@@ -3651,13 +3611,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B135" t="n">
         <v>1</v>
       </c>
       <c r="C135" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D135" t="n">
         <v>4138480</v>
@@ -3674,13 +3634,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B136" t="n">
         <v>2</v>
       </c>
       <c r="C136" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D136" t="n">
         <v>5574634</v>
@@ -3697,13 +3657,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B137" t="n">
         <v>3</v>
       </c>
       <c r="C137" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D137" t="n">
         <v>3394070</v>
@@ -3720,13 +3680,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B138" t="n">
         <v>85</v>
       </c>
       <c r="C138" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D138" t="n">
         <v>186527</v>
@@ -3743,13 +3703,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B139" t="n">
         <v>88</v>
       </c>
       <c r="C139" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D139" t="n">
         <v>2136</v>
@@ -3766,13 +3726,13 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B140" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>211</v>
@@ -3789,13 +3749,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B141" t="n">
         <v>1</v>
       </c>
       <c r="C141" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D141" t="n">
         <v>10296748</v>
@@ -3812,13 +3772,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B142" t="n">
         <v>2</v>
       </c>
       <c r="C142" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D142" t="n">
         <v>1763276</v>
@@ -3835,13 +3795,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B143" t="n">
         <v>3</v>
       </c>
       <c r="C143" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D143" t="n">
         <v>1211052</v>
@@ -3858,13 +3818,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B144" t="n">
         <v>85</v>
       </c>
       <c r="C144" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D144" t="n">
         <v>23947</v>
@@ -3881,13 +3841,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B145" t="n">
         <v>88</v>
       </c>
       <c r="C145" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D145" t="n">
         <v>866</v>
@@ -3904,13 +3864,13 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B146" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>169</v>
@@ -3927,13 +3887,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B147" t="n">
         <v>1</v>
       </c>
       <c r="C147" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D147" t="n">
         <v>5835997</v>
@@ -3950,13 +3910,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B148" t="n">
         <v>2</v>
       </c>
       <c r="C148" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D148" t="n">
         <v>3008974</v>
@@ -3973,13 +3933,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B149" t="n">
         <v>3</v>
       </c>
       <c r="C149" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D149" t="n">
         <v>3969197</v>
@@ -3996,13 +3956,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B150" t="n">
         <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D150" t="n">
         <v>441454</v>
@@ -4019,13 +3979,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B151" t="n">
         <v>5</v>
       </c>
       <c r="C151" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D151" t="n">
         <v>17381</v>
@@ -4042,13 +4002,13 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B152" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>23055</v>
@@ -4065,13 +4025,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B153" t="n">
         <v>1</v>
       </c>
       <c r="C153" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D153" t="n">
         <v>1824589</v>
@@ -4088,13 +4048,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B154" t="n">
         <v>2</v>
       </c>
       <c r="C154" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D154" t="n">
         <v>6465234</v>
@@ -4111,13 +4071,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B155" t="n">
         <v>3</v>
       </c>
       <c r="C155" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D155" t="n">
         <v>4999850</v>
@@ -4134,13 +4094,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B156" t="n">
         <v>85</v>
       </c>
       <c r="C156" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D156" t="n">
         <v>6216</v>
@@ -4157,13 +4117,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B157" t="n">
         <v>88</v>
       </c>
       <c r="C157" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -4180,13 +4140,13 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B158" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>169</v>
@@ -4203,13 +4163,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B159" t="n">
         <v>0</v>
       </c>
       <c r="C159" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D159" t="n">
         <v>6295807</v>
@@ -4226,13 +4186,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B160" t="n">
         <v>1</v>
       </c>
       <c r="C160" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D160" t="n">
         <v>6627002</v>
@@ -4249,13 +4209,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B161" t="n">
         <v>88</v>
       </c>
       <c r="C161" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D161" t="n">
         <v>349411</v>
@@ -4272,13 +4232,13 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B162" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>23033</v>
@@ -4295,13 +4255,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B163" t="n">
         <v>1</v>
       </c>
       <c r="C163" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D163" t="n">
         <v>1088781</v>
@@ -4318,13 +4278,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B164" t="n">
         <v>2</v>
       </c>
       <c r="C164" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D164" t="n">
         <v>6660299</v>
@@ -4341,13 +4301,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B165" t="n">
         <v>3</v>
       </c>
       <c r="C165" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D165" t="n">
         <v>5523433</v>
@@ -4364,13 +4324,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B166" t="n">
         <v>85</v>
       </c>
       <c r="C166" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -4387,13 +4347,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B167" t="n">
         <v>88</v>
       </c>
       <c r="C167" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D167" t="n">
         <v>9270</v>
@@ -4410,13 +4370,13 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B168" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>14275</v>
@@ -4433,13 +4393,13 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B169" t="n">
         <v>1</v>
       </c>
       <c r="C169" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D169" t="n">
         <v>3267358</v>
@@ -4456,13 +4416,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B170" t="n">
         <v>2</v>
       </c>
       <c r="C170" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D170" t="n">
         <v>3603876</v>
@@ -4479,13 +4439,13 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B171" t="n">
         <v>3</v>
       </c>
       <c r="C171" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D171" t="n">
         <v>6039957</v>
@@ -4502,13 +4462,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B172" t="n">
         <v>85</v>
       </c>
       <c r="C172" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -4525,13 +4485,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B173" t="n">
         <v>88</v>
       </c>
       <c r="C173" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D173" t="n">
         <v>371956</v>
@@ -4548,13 +4508,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B174" t="n">
         <v>99</v>
       </c>
       <c r="C174" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D174" t="n">
         <v>12911</v>

--- a/output/tables/2025/tabla2_variables_fuente.xlsx
+++ b/output/tables/2025/tabla2_variables_fuente.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -48,12 +48,6 @@
   </si>
   <si>
     <t xml:space="preserve">comper_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comgen_per_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comgen_com_pct</t>
   </si>
   <si>
     <t xml:space="preserve">emper_ep_pct_cat</t>
@@ -3039,22 +3033,22 @@
         <v>12</v>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C110" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D110" t="n">
-        <v>1088781</v>
+        <v>2252060</v>
       </c>
       <c r="E110" t="n">
-        <v>8.2</v>
+        <v>16.94</v>
       </c>
       <c r="F110" t="n">
-        <v>8.2</v>
+        <v>16.94</v>
       </c>
       <c r="G110" t="n">
-        <v>8.2</v>
+        <v>16.94</v>
       </c>
     </row>
     <row r="111">
@@ -3062,22 +3056,22 @@
         <v>12</v>
       </c>
       <c r="B111" t="n">
-        <v>11.11</v>
+        <v>2</v>
       </c>
       <c r="C111" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D111" t="n">
-        <v>3103365</v>
+        <v>5900237</v>
       </c>
       <c r="E111" t="n">
-        <v>23.38</v>
+        <v>44.38</v>
       </c>
       <c r="F111" t="n">
-        <v>23.38</v>
+        <v>44.38</v>
       </c>
       <c r="G111" t="n">
-        <v>31.59</v>
+        <v>61.31</v>
       </c>
     </row>
     <row r="112">
@@ -3085,22 +3079,22 @@
         <v>12</v>
       </c>
       <c r="B112" t="n">
-        <v>22.22</v>
+        <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D112" t="n">
-        <v>3556934</v>
+        <v>5118761</v>
       </c>
       <c r="E112" t="n">
-        <v>26.8</v>
+        <v>38.5</v>
       </c>
       <c r="F112" t="n">
-        <v>26.8</v>
+        <v>38.5</v>
       </c>
       <c r="G112" t="n">
-        <v>58.38</v>
+        <v>99.81</v>
       </c>
     </row>
     <row r="113">
@@ -3108,22 +3102,22 @@
         <v>12</v>
       </c>
       <c r="B113" t="n">
-        <v>33.33</v>
+        <v>85</v>
       </c>
       <c r="C113" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D113" t="n">
-        <v>2631062</v>
+        <v>24831</v>
       </c>
       <c r="E113" t="n">
-        <v>19.82</v>
+        <v>0.19</v>
       </c>
       <c r="F113" t="n">
-        <v>19.82</v>
+        <v>0.19</v>
       </c>
       <c r="G113" t="n">
-        <v>78.21</v>
+        <v>100</v>
       </c>
     </row>
     <row r="114">
@@ -3131,1401 +3125,964 @@
         <v>12</v>
       </c>
       <c r="B114" t="n">
-        <v>44.44</v>
+        <v>88</v>
       </c>
       <c r="C114" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D114" t="n">
-        <v>1528379</v>
+        <v>0</v>
       </c>
       <c r="E114" t="n">
-        <v>11.52</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>11.52</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>89.72</v>
+        <v>100</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="s">
+      <c r="A115" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B115" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="C115" t="s">
-        <v>8</v>
-      </c>
-      <c r="D115" t="n">
-        <v>782192</v>
-      </c>
-      <c r="E115" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="F115" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="G115" t="n">
-        <v>95.62</v>
+      <c r="B115" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B116" t="n">
-        <v>66.67</v>
+        <v>1</v>
       </c>
       <c r="C116" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D116" t="n">
-        <v>381157</v>
+        <v>4138480</v>
       </c>
       <c r="E116" t="n">
-        <v>2.87</v>
+        <v>31.13</v>
       </c>
       <c r="F116" t="n">
-        <v>2.87</v>
+        <v>31.13</v>
       </c>
       <c r="G116" t="n">
-        <v>98.49</v>
+        <v>31.13</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B117" t="n">
-        <v>77.78</v>
+        <v>2</v>
       </c>
       <c r="C117" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D117" t="n">
-        <v>162624</v>
+        <v>5574634</v>
       </c>
       <c r="E117" t="n">
-        <v>1.23</v>
+        <v>41.93</v>
       </c>
       <c r="F117" t="n">
-        <v>1.23</v>
+        <v>41.93</v>
       </c>
       <c r="G117" t="n">
-        <v>99.71</v>
+        <v>73.05</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B118" t="n">
-        <v>88.89</v>
+        <v>3</v>
       </c>
       <c r="C118" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D118" t="n">
-        <v>36088</v>
+        <v>3394070</v>
       </c>
       <c r="E118" t="n">
-        <v>0.27</v>
+        <v>25.53</v>
       </c>
       <c r="F118" t="n">
-        <v>0.27</v>
+        <v>25.53</v>
       </c>
       <c r="G118" t="n">
-        <v>99.99</v>
+        <v>98.58</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B119" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>1931</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>100</v>
+      <c r="A119" t="s">
+        <v>19</v>
+      </c>
+      <c r="B119" t="n">
+        <v>85</v>
+      </c>
+      <c r="C119" t="s">
+        <v>16</v>
+      </c>
+      <c r="D119" t="n">
+        <v>186527</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G119" t="n">
+        <v>99.98</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B120" t="n">
+        <v>88</v>
+      </c>
+      <c r="C120" t="s">
+        <v>17</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2136</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G120" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="E121" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C120" t="s">
-        <v>8</v>
-      </c>
-      <c r="D120" t="n">
-        <v>3267358</v>
-      </c>
-      <c r="E120" t="n">
-        <v>25.31</v>
-      </c>
-      <c r="F120" t="n">
-        <v>25.31</v>
-      </c>
-      <c r="G120" t="n">
-        <v>25.31</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>13</v>
-      </c>
-      <c r="B121" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="C121" t="s">
-        <v>8</v>
-      </c>
-      <c r="D121" t="n">
-        <v>3603876</v>
-      </c>
-      <c r="E121" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="F121" t="n">
-        <v>27.91</v>
-      </c>
-      <c r="G121" t="n">
-        <v>53.22</v>
+      <c r="F121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B122" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D122" t="n">
-        <v>2923576</v>
+        <v>10296748</v>
       </c>
       <c r="E122" t="n">
-        <v>22.64</v>
+        <v>77.44</v>
       </c>
       <c r="F122" t="n">
-        <v>22.64</v>
+        <v>77.44</v>
       </c>
       <c r="G122" t="n">
-        <v>75.86</v>
+        <v>77.44</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B123" t="n">
-        <v>37.5</v>
+        <v>2</v>
       </c>
       <c r="C123" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D123" t="n">
-        <v>1706426</v>
+        <v>1763276</v>
       </c>
       <c r="E123" t="n">
-        <v>13.22</v>
+        <v>13.26</v>
       </c>
       <c r="F123" t="n">
-        <v>13.22</v>
+        <v>13.26</v>
       </c>
       <c r="G123" t="n">
-        <v>89.08</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B124" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D124" t="n">
-        <v>805341</v>
+        <v>1211052</v>
       </c>
       <c r="E124" t="n">
-        <v>6.24</v>
+        <v>9.11</v>
       </c>
       <c r="F124" t="n">
-        <v>6.24</v>
+        <v>9.11</v>
       </c>
       <c r="G124" t="n">
-        <v>95.32</v>
+        <v>99.81</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B125" t="n">
-        <v>62.5</v>
+        <v>85</v>
       </c>
       <c r="C125" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D125" t="n">
-        <v>418863</v>
+        <v>23947</v>
       </c>
       <c r="E125" t="n">
-        <v>3.24</v>
+        <v>0.18</v>
       </c>
       <c r="F125" t="n">
-        <v>3.24</v>
+        <v>0.18</v>
       </c>
       <c r="G125" t="n">
-        <v>98.56</v>
+        <v>99.99</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B126" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C126" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D126" t="n">
-        <v>152816</v>
+        <v>866</v>
       </c>
       <c r="E126" t="n">
-        <v>1.18</v>
+        <v>0.01</v>
       </c>
       <c r="F126" t="n">
-        <v>1.18</v>
+        <v>0.01</v>
       </c>
       <c r="G126" t="n">
-        <v>99.74</v>
+        <v>100</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="s">
-        <v>13</v>
-      </c>
-      <c r="B127" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="C127" t="s">
-        <v>8</v>
-      </c>
-      <c r="D127" t="n">
-        <v>29418</v>
-      </c>
-      <c r="E127" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="F127" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="G127" t="n">
-        <v>99.97</v>
+      <c r="A127" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B128" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D128" s="2" t="n">
-        <v>3517</v>
-      </c>
-      <c r="E128" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>100</v>
+      <c r="A128" t="s">
+        <v>27</v>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="s">
+        <v>28</v>
+      </c>
+      <c r="D128" t="n">
+        <v>5835997</v>
+      </c>
+      <c r="E128" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="F128" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="G128" t="n">
+        <v>43.89</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D129" t="n">
-        <v>2252060</v>
+        <v>3008974</v>
       </c>
       <c r="E129" t="n">
-        <v>16.94</v>
+        <v>22.63</v>
       </c>
       <c r="F129" t="n">
-        <v>16.94</v>
+        <v>22.63</v>
       </c>
       <c r="G129" t="n">
-        <v>16.94</v>
+        <v>66.52</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C130" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D130" t="n">
-        <v>5900237</v>
+        <v>3969197</v>
       </c>
       <c r="E130" t="n">
-        <v>44.38</v>
+        <v>29.85</v>
       </c>
       <c r="F130" t="n">
-        <v>44.38</v>
+        <v>29.85</v>
       </c>
       <c r="G130" t="n">
-        <v>61.31</v>
+        <v>96.38</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B131" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D131" t="n">
-        <v>5118761</v>
+        <v>441454</v>
       </c>
       <c r="E131" t="n">
-        <v>38.5</v>
+        <v>3.32</v>
       </c>
       <c r="F131" t="n">
-        <v>38.5</v>
+        <v>3.32</v>
       </c>
       <c r="G131" t="n">
-        <v>99.81</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B132" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="C132" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D132" t="n">
-        <v>24831</v>
+        <v>17381</v>
       </c>
       <c r="E132" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="F132" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="G132" t="n">
+        <v>99.83</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>23055</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G133" s="2" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>14</v>
-      </c>
-      <c r="B133" t="n">
-        <v>88</v>
-      </c>
-      <c r="C133" t="s">
-        <v>19</v>
-      </c>
-      <c r="D133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" t="n">
-        <v>100</v>
-      </c>
-    </row>
     <row r="134">
-      <c r="A134" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B134" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D134" s="2" t="n">
-        <v>169</v>
-      </c>
-      <c r="E134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>100</v>
+      <c r="A134" t="s">
+        <v>34</v>
+      </c>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" t="s">
+        <v>35</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1824589</v>
+      </c>
+      <c r="E134" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="F134" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="G134" t="n">
+        <v>13.72</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D135" t="n">
-        <v>4138480</v>
+        <v>6465234</v>
       </c>
       <c r="E135" t="n">
-        <v>31.13</v>
+        <v>48.63</v>
       </c>
       <c r="F135" t="n">
-        <v>31.13</v>
+        <v>48.63</v>
       </c>
       <c r="G135" t="n">
-        <v>31.13</v>
+        <v>62.35</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C136" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D136" t="n">
-        <v>5574634</v>
+        <v>4999850</v>
       </c>
       <c r="E136" t="n">
-        <v>41.93</v>
+        <v>37.6</v>
       </c>
       <c r="F136" t="n">
-        <v>41.93</v>
+        <v>37.6</v>
       </c>
       <c r="G136" t="n">
-        <v>73.05</v>
+        <v>99.95</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B137" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="C137" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D137" t="n">
-        <v>3394070</v>
+        <v>6216</v>
       </c>
       <c r="E137" t="n">
-        <v>25.53</v>
+        <v>0.05</v>
       </c>
       <c r="F137" t="n">
-        <v>25.53</v>
+        <v>0.05</v>
       </c>
       <c r="G137" t="n">
-        <v>98.58</v>
+        <v>100</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B138" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C138" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C139" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D138" t="n">
-        <v>186527</v>
-      </c>
-      <c r="E138" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F138" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G138" t="n">
-        <v>99.98</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>21</v>
-      </c>
-      <c r="B139" t="n">
-        <v>88</v>
-      </c>
-      <c r="C139" t="s">
-        <v>19</v>
-      </c>
-      <c r="D139" t="n">
-        <v>2136</v>
-      </c>
-      <c r="E139" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F139" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G139" t="n">
+      <c r="D139" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B140" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D140" s="2" t="n">
-        <v>211</v>
-      </c>
-      <c r="E140" s="2" t="n">
+      <c r="A140" t="s">
+        <v>38</v>
+      </c>
+      <c r="B140" t="n">
         <v>0</v>
       </c>
-      <c r="F140" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>100</v>
+      <c r="C140" t="s">
+        <v>39</v>
+      </c>
+      <c r="D140" t="n">
+        <v>6295807</v>
+      </c>
+      <c r="E140" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="F140" t="n">
+        <v>47.35</v>
+      </c>
+      <c r="G140" t="n">
+        <v>47.35</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B141" t="n">
         <v>1</v>
       </c>
       <c r="C141" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D141" t="n">
-        <v>10296748</v>
+        <v>6627002</v>
       </c>
       <c r="E141" t="n">
-        <v>77.44</v>
+        <v>49.84</v>
       </c>
       <c r="F141" t="n">
-        <v>77.44</v>
+        <v>49.84</v>
       </c>
       <c r="G141" t="n">
-        <v>77.44</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B142" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="C142" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D142" t="n">
-        <v>1763276</v>
+        <v>349411</v>
       </c>
       <c r="E142" t="n">
-        <v>13.26</v>
+        <v>2.63</v>
       </c>
       <c r="F142" t="n">
-        <v>13.26</v>
+        <v>2.63</v>
       </c>
       <c r="G142" t="n">
-        <v>90.7</v>
+        <v>99.83</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="s">
-        <v>25</v>
-      </c>
-      <c r="B143" t="n">
-        <v>3</v>
-      </c>
-      <c r="C143" t="s">
-        <v>28</v>
-      </c>
-      <c r="D143" t="n">
-        <v>1211052</v>
-      </c>
-      <c r="E143" t="n">
-        <v>9.11</v>
-      </c>
-      <c r="F143" t="n">
-        <v>9.11</v>
-      </c>
-      <c r="G143" t="n">
-        <v>99.81</v>
+      <c r="A143" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>23033</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B144" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="C144" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D144" t="n">
-        <v>23947</v>
+        <v>1088781</v>
       </c>
       <c r="E144" t="n">
-        <v>0.18</v>
+        <v>8.19</v>
       </c>
       <c r="F144" t="n">
-        <v>0.18</v>
+        <v>8.19</v>
       </c>
       <c r="G144" t="n">
-        <v>99.99</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B145" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="C145" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D145" t="n">
-        <v>866</v>
+        <v>6660299</v>
       </c>
       <c r="E145" t="n">
-        <v>0.01</v>
+        <v>50.09</v>
       </c>
       <c r="F145" t="n">
-        <v>0.01</v>
+        <v>50.09</v>
       </c>
       <c r="G145" t="n">
-        <v>100</v>
+        <v>58.28</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B146" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D146" s="2" t="n">
-        <v>169</v>
-      </c>
-      <c r="E146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>100</v>
+      <c r="A146" t="s">
+        <v>41</v>
+      </c>
+      <c r="B146" t="n">
+        <v>3</v>
+      </c>
+      <c r="C146" t="s">
+        <v>44</v>
+      </c>
+      <c r="D146" t="n">
+        <v>5523433</v>
+      </c>
+      <c r="E146" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="F146" t="n">
+        <v>41.54</v>
+      </c>
+      <c r="G146" t="n">
+        <v>99.82</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="C147" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D147" t="n">
-        <v>5835997</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>43.89</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>43.89</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>43.89</v>
+        <v>99.82</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B148" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="C148" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D148" t="n">
-        <v>3008974</v>
+        <v>9270</v>
       </c>
       <c r="E148" t="n">
-        <v>22.63</v>
+        <v>0.07</v>
       </c>
       <c r="F148" t="n">
-        <v>22.63</v>
+        <v>0.07</v>
       </c>
       <c r="G148" t="n">
-        <v>66.52</v>
+        <v>99.89</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="s">
-        <v>29</v>
-      </c>
-      <c r="B149" t="n">
-        <v>3</v>
-      </c>
-      <c r="C149" t="s">
-        <v>32</v>
-      </c>
-      <c r="D149" t="n">
-        <v>3969197</v>
-      </c>
-      <c r="E149" t="n">
-        <v>29.85</v>
-      </c>
-      <c r="F149" t="n">
-        <v>29.85</v>
-      </c>
-      <c r="G149" t="n">
-        <v>96.38</v>
+      <c r="A149" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>14275</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B150" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C150" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D150" t="n">
-        <v>441454</v>
+        <v>3267358</v>
       </c>
       <c r="E150" t="n">
-        <v>3.32</v>
+        <v>24.57</v>
       </c>
       <c r="F150" t="n">
-        <v>3.32</v>
+        <v>24.57</v>
       </c>
       <c r="G150" t="n">
-        <v>99.7</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B151" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C151" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D151" t="n">
-        <v>17381</v>
+        <v>3603876</v>
       </c>
       <c r="E151" t="n">
-        <v>0.13</v>
+        <v>27.1</v>
       </c>
       <c r="F151" t="n">
-        <v>0.13</v>
+        <v>27.1</v>
       </c>
       <c r="G151" t="n">
-        <v>99.83</v>
+        <v>51.68</v>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B152" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D152" s="2" t="n">
-        <v>23055</v>
-      </c>
-      <c r="E152" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>100</v>
+      <c r="A152" t="s">
+        <v>45</v>
+      </c>
+      <c r="B152" t="n">
+        <v>3</v>
+      </c>
+      <c r="C152" t="s">
+        <v>48</v>
+      </c>
+      <c r="D152" t="n">
+        <v>6039957</v>
+      </c>
+      <c r="E152" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="F152" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="G152" t="n">
+        <v>97.11</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B153" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="C153" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D153" t="n">
-        <v>1824589</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>13.72</v>
+        <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>13.72</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>13.72</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B154" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="C154" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D154" t="n">
-        <v>6465234</v>
+        <v>371956</v>
       </c>
       <c r="E154" t="n">
-        <v>48.63</v>
+        <v>2.8</v>
       </c>
       <c r="F154" t="n">
-        <v>48.63</v>
+        <v>2.8</v>
       </c>
       <c r="G154" t="n">
-        <v>62.35</v>
+        <v>99.9</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B155" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="C155" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D155" t="n">
-        <v>4999850</v>
+        <v>12911</v>
       </c>
       <c r="E155" t="n">
-        <v>37.6</v>
+        <v>0.1</v>
       </c>
       <c r="F155" t="n">
-        <v>37.6</v>
+        <v>0.1</v>
       </c>
       <c r="G155" t="n">
-        <v>99.95</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>36</v>
-      </c>
-      <c r="B156" t="n">
-        <v>85</v>
-      </c>
-      <c r="C156" t="s">
-        <v>18</v>
-      </c>
-      <c r="D156" t="n">
-        <v>6216</v>
-      </c>
-      <c r="E156" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G156" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>36</v>
-      </c>
-      <c r="B157" t="n">
-        <v>88</v>
-      </c>
-      <c r="C157" t="s">
-        <v>19</v>
-      </c>
-      <c r="D157" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B158" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D158" s="2" t="n">
-        <v>169</v>
-      </c>
-      <c r="E158" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" s="2" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>40</v>
-      </c>
-      <c r="B159" t="n">
-        <v>0</v>
-      </c>
-      <c r="C159" t="s">
-        <v>41</v>
-      </c>
-      <c r="D159" t="n">
-        <v>6295807</v>
-      </c>
-      <c r="E159" t="n">
-        <v>47.35</v>
-      </c>
-      <c r="F159" t="n">
-        <v>47.35</v>
-      </c>
-      <c r="G159" t="n">
-        <v>47.35</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>40</v>
-      </c>
-      <c r="B160" t="n">
-        <v>1</v>
-      </c>
-      <c r="C160" t="s">
-        <v>42</v>
-      </c>
-      <c r="D160" t="n">
-        <v>6627002</v>
-      </c>
-      <c r="E160" t="n">
-        <v>49.84</v>
-      </c>
-      <c r="F160" t="n">
-        <v>49.84</v>
-      </c>
-      <c r="G160" t="n">
-        <v>97.2</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>40</v>
-      </c>
-      <c r="B161" t="n">
-        <v>88</v>
-      </c>
-      <c r="C161" t="s">
-        <v>19</v>
-      </c>
-      <c r="D161" t="n">
-        <v>349411</v>
-      </c>
-      <c r="E161" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="F161" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="G161" t="n">
-        <v>99.83</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B162" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D162" s="2" t="n">
-        <v>23033</v>
-      </c>
-      <c r="E162" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F162" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G162" s="2" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>43</v>
-      </c>
-      <c r="B163" t="n">
-        <v>1</v>
-      </c>
-      <c r="C163" t="s">
-        <v>44</v>
-      </c>
-      <c r="D163" t="n">
-        <v>1088781</v>
-      </c>
-      <c r="E163" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="F163" t="n">
-        <v>8.19</v>
-      </c>
-      <c r="G163" t="n">
-        <v>8.19</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>43</v>
-      </c>
-      <c r="B164" t="n">
-        <v>2</v>
-      </c>
-      <c r="C164" t="s">
-        <v>45</v>
-      </c>
-      <c r="D164" t="n">
-        <v>6660299</v>
-      </c>
-      <c r="E164" t="n">
-        <v>50.09</v>
-      </c>
-      <c r="F164" t="n">
-        <v>50.09</v>
-      </c>
-      <c r="G164" t="n">
-        <v>58.28</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>43</v>
-      </c>
-      <c r="B165" t="n">
-        <v>3</v>
-      </c>
-      <c r="C165" t="s">
-        <v>46</v>
-      </c>
-      <c r="D165" t="n">
-        <v>5523433</v>
-      </c>
-      <c r="E165" t="n">
-        <v>41.54</v>
-      </c>
-      <c r="F165" t="n">
-        <v>41.54</v>
-      </c>
-      <c r="G165" t="n">
-        <v>99.82</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>43</v>
-      </c>
-      <c r="B166" t="n">
-        <v>85</v>
-      </c>
-      <c r="C166" t="s">
-        <v>18</v>
-      </c>
-      <c r="D166" t="n">
-        <v>0</v>
-      </c>
-      <c r="E166" t="n">
-        <v>0</v>
-      </c>
-      <c r="F166" t="n">
-        <v>0</v>
-      </c>
-      <c r="G166" t="n">
-        <v>99.82</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>43</v>
-      </c>
-      <c r="B167" t="n">
-        <v>88</v>
-      </c>
-      <c r="C167" t="s">
-        <v>19</v>
-      </c>
-      <c r="D167" t="n">
-        <v>9270</v>
-      </c>
-      <c r="E167" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="F167" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="G167" t="n">
-        <v>99.89</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B168" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D168" s="2" t="n">
-        <v>14275</v>
-      </c>
-      <c r="E168" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F168" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G168" s="2" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>47</v>
-      </c>
-      <c r="B169" t="n">
-        <v>1</v>
-      </c>
-      <c r="C169" t="s">
-        <v>48</v>
-      </c>
-      <c r="D169" t="n">
-        <v>3267358</v>
-      </c>
-      <c r="E169" t="n">
-        <v>24.57</v>
-      </c>
-      <c r="F169" t="n">
-        <v>24.57</v>
-      </c>
-      <c r="G169" t="n">
-        <v>24.57</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>47</v>
-      </c>
-      <c r="B170" t="n">
-        <v>2</v>
-      </c>
-      <c r="C170" t="s">
-        <v>49</v>
-      </c>
-      <c r="D170" t="n">
-        <v>3603876</v>
-      </c>
-      <c r="E170" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="F170" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="G170" t="n">
-        <v>51.68</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>47</v>
-      </c>
-      <c r="B171" t="n">
-        <v>3</v>
-      </c>
-      <c r="C171" t="s">
-        <v>50</v>
-      </c>
-      <c r="D171" t="n">
-        <v>6039957</v>
-      </c>
-      <c r="E171" t="n">
-        <v>45.43</v>
-      </c>
-      <c r="F171" t="n">
-        <v>45.43</v>
-      </c>
-      <c r="G171" t="n">
-        <v>97.11</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>47</v>
-      </c>
-      <c r="B172" t="n">
-        <v>85</v>
-      </c>
-      <c r="C172" t="s">
-        <v>18</v>
-      </c>
-      <c r="D172" t="n">
-        <v>0</v>
-      </c>
-      <c r="E172" t="n">
-        <v>0</v>
-      </c>
-      <c r="F172" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" t="n">
-        <v>97.11</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>47</v>
-      </c>
-      <c r="B173" t="n">
-        <v>88</v>
-      </c>
-      <c r="C173" t="s">
-        <v>19</v>
-      </c>
-      <c r="D173" t="n">
-        <v>371956</v>
-      </c>
-      <c r="E173" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F173" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G173" t="n">
-        <v>99.9</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>47</v>
-      </c>
-      <c r="B174" t="n">
-        <v>99</v>
-      </c>
-      <c r="C174" t="s">
-        <v>20</v>
-      </c>
-      <c r="D174" t="n">
-        <v>12911</v>
-      </c>
-      <c r="E174" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G174" t="n">
         <v>100</v>
       </c>
     </row>

--- a/output/tables/2025/tabla2_variables_fuente.xlsx
+++ b/output/tables/2025/tabla2_variables_fuente.xlsx
@@ -35,18 +35,18 @@
     <t xml:space="preserve">cum.prc</t>
   </si>
   <si>
+    <t xml:space="preserve">emper_barrio_pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;none&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emper_casa_pct</t>
+  </si>
+  <si>
     <t xml:space="preserve">emper_ep_pct</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;none&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emper_barrio_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emper_casa_pct</t>
-  </si>
-  <si>
     <t xml:space="preserve">comper_pct</t>
   </si>
   <si>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">Gasta en medidas de seguridad</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_per_pct_cat</t>
+    <t xml:space="preserve">comgen_per_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Sin medidas en la vivienda</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">Tres o más medidas en la vivienda</t>
   </si>
   <si>
-    <t xml:space="preserve">comgen_com_pct_cat</t>
+    <t xml:space="preserve">comgen_com_cat</t>
   </si>
   <si>
     <t xml:space="preserve">Sin medidas en el barrio</t>
@@ -555,16 +555,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>2252229</v>
+        <v>4140827</v>
       </c>
       <c r="E2" t="n">
-        <v>16.97</v>
+        <v>31.59</v>
       </c>
       <c r="F2" t="n">
-        <v>16.97</v>
+        <v>31.59</v>
       </c>
       <c r="G2" t="n">
-        <v>16.97</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="3">
@@ -572,1034 +572,1034 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>9.09</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>189986</v>
+        <v>5574634</v>
       </c>
       <c r="E3" t="n">
-        <v>1.43</v>
+        <v>42.52</v>
       </c>
       <c r="F3" t="n">
-        <v>1.43</v>
+        <v>42.52</v>
       </c>
       <c r="G3" t="n">
-        <v>18.4</v>
+        <v>74.11</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="n">
-        <v>240524</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="G4" t="n">
-        <v>20.21</v>
+      <c r="B4" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3394070</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>228697</v>
+        <v>10297783</v>
       </c>
       <c r="E5" t="n">
-        <v>1.72</v>
+        <v>77.59</v>
       </c>
       <c r="F5" t="n">
-        <v>1.72</v>
+        <v>77.59</v>
       </c>
       <c r="G5" t="n">
-        <v>21.94</v>
+        <v>77.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>234180</v>
+        <v>1763276</v>
       </c>
       <c r="E6" t="n">
-        <v>1.76</v>
+        <v>13.29</v>
       </c>
       <c r="F6" t="n">
-        <v>1.76</v>
+        <v>13.29</v>
       </c>
       <c r="G6" t="n">
-        <v>23.7</v>
+        <v>90.88</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="n">
-        <v>14.29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="n">
-        <v>253819</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="G7" t="n">
-        <v>25.62</v>
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1211052</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>9.12</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>9.12</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>204454</v>
+        <v>2252229</v>
       </c>
       <c r="E8" t="n">
-        <v>1.54</v>
+        <v>16.97</v>
       </c>
       <c r="F8" t="n">
-        <v>1.54</v>
+        <v>16.97</v>
       </c>
       <c r="G8" t="n">
-        <v>27.16</v>
+        <v>16.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>18.18</v>
+        <v>9.09</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>192674</v>
+        <v>189986</v>
       </c>
       <c r="E9" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="F9" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="G9" t="n">
-        <v>28.61</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>368947</v>
+        <v>240524</v>
       </c>
       <c r="E10" t="n">
-        <v>2.78</v>
+        <v>1.81</v>
       </c>
       <c r="F10" t="n">
-        <v>2.78</v>
+        <v>1.81</v>
       </c>
       <c r="G10" t="n">
-        <v>31.39</v>
+        <v>20.21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>22.22</v>
+        <v>11.11</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>215346</v>
+        <v>228697</v>
       </c>
       <c r="E11" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="F11" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="G11" t="n">
-        <v>33.01</v>
+        <v>21.94</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>333553</v>
+        <v>234180</v>
       </c>
       <c r="E12" t="n">
-        <v>2.51</v>
+        <v>1.76</v>
       </c>
       <c r="F12" t="n">
-        <v>2.51</v>
+        <v>1.76</v>
       </c>
       <c r="G12" t="n">
-        <v>35.52</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B13" t="n">
-        <v>27.27</v>
+        <v>14.29</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>183444</v>
+        <v>253819</v>
       </c>
       <c r="E13" t="n">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="F13" t="n">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="G13" t="n">
-        <v>36.91</v>
+        <v>25.62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B14" t="n">
-        <v>28.57</v>
+        <v>16.67</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>225584</v>
+        <v>204454</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="G14" t="n">
-        <v>38.61</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B15" t="n">
-        <v>30</v>
+        <v>18.18</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>238492</v>
+        <v>192674</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="G15" t="n">
-        <v>40.4</v>
+        <v>28.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B16" t="n">
-        <v>33.33</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>491627</v>
+        <v>368947</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7</v>
+        <v>2.78</v>
       </c>
       <c r="F16" t="n">
-        <v>3.7</v>
+        <v>2.78</v>
       </c>
       <c r="G16" t="n">
-        <v>44.11</v>
+        <v>31.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B17" t="n">
-        <v>36.36</v>
+        <v>22.22</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>226347</v>
+        <v>215346</v>
       </c>
       <c r="E17" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="F17" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="G17" t="n">
-        <v>45.81</v>
+        <v>33.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B18" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>215680</v>
+        <v>333553</v>
       </c>
       <c r="E18" t="n">
-        <v>1.63</v>
+        <v>2.51</v>
       </c>
       <c r="F18" t="n">
-        <v>1.63</v>
+        <v>2.51</v>
       </c>
       <c r="G18" t="n">
-        <v>47.44</v>
+        <v>35.52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B19" t="n">
-        <v>40</v>
+        <v>27.27</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>380926</v>
+        <v>183444</v>
       </c>
       <c r="E19" t="n">
-        <v>2.87</v>
+        <v>1.38</v>
       </c>
       <c r="F19" t="n">
-        <v>2.87</v>
+        <v>1.38</v>
       </c>
       <c r="G19" t="n">
-        <v>50.31</v>
+        <v>36.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B20" t="n">
-        <v>42.86</v>
+        <v>28.57</v>
       </c>
       <c r="C20" t="s">
         <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>222450</v>
+        <v>225584</v>
       </c>
       <c r="E20" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="F20" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G20" t="n">
-        <v>51.98</v>
+        <v>38.61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B21" t="n">
-        <v>44.44</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>223503</v>
+        <v>238492</v>
       </c>
       <c r="E21" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="F21" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="G21" t="n">
-        <v>53.67</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B22" t="n">
-        <v>45.45</v>
+        <v>33.33</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>230028</v>
+        <v>491627</v>
       </c>
       <c r="E22" t="n">
-        <v>1.73</v>
+        <v>3.7</v>
       </c>
       <c r="F22" t="n">
-        <v>1.73</v>
+        <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>55.4</v>
+        <v>44.11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B23" t="n">
-        <v>50</v>
+        <v>36.36</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>799975</v>
+        <v>226347</v>
       </c>
       <c r="E23" t="n">
-        <v>6.03</v>
+        <v>1.71</v>
       </c>
       <c r="F23" t="n">
-        <v>6.03</v>
+        <v>1.71</v>
       </c>
       <c r="G23" t="n">
-        <v>61.43</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B24" t="n">
-        <v>54.55</v>
+        <v>37.5</v>
       </c>
       <c r="C24" t="s">
         <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>231453</v>
+        <v>215680</v>
       </c>
       <c r="E24" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="F24" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="G24" t="n">
-        <v>63.17</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B25" t="n">
-        <v>55.56</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
         <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>226334</v>
+        <v>380926</v>
       </c>
       <c r="E25" t="n">
-        <v>1.71</v>
+        <v>2.87</v>
       </c>
       <c r="F25" t="n">
-        <v>1.71</v>
+        <v>2.87</v>
       </c>
       <c r="G25" t="n">
-        <v>64.88</v>
+        <v>50.31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B26" t="n">
-        <v>57.14</v>
+        <v>42.86</v>
       </c>
       <c r="C26" t="s">
         <v>8</v>
       </c>
       <c r="D26" t="n">
-        <v>204906</v>
+        <v>222450</v>
       </c>
       <c r="E26" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="F26" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="G26" t="n">
-        <v>66.42</v>
+        <v>51.98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B27" t="n">
-        <v>60</v>
+        <v>44.44</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>360984</v>
+        <v>223503</v>
       </c>
       <c r="E27" t="n">
-        <v>2.72</v>
+        <v>1.68</v>
       </c>
       <c r="F27" t="n">
-        <v>2.72</v>
+        <v>1.68</v>
       </c>
       <c r="G27" t="n">
-        <v>69.14</v>
+        <v>53.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B28" t="n">
-        <v>62.5</v>
+        <v>45.45</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>211198</v>
+        <v>230028</v>
       </c>
       <c r="E28" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="F28" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="G28" t="n">
-        <v>70.73</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B29" t="n">
-        <v>63.64</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="n">
-        <v>214916</v>
+        <v>799975</v>
       </c>
       <c r="E29" t="n">
-        <v>1.62</v>
+        <v>6.03</v>
       </c>
       <c r="F29" t="n">
-        <v>1.62</v>
+        <v>6.03</v>
       </c>
       <c r="G29" t="n">
-        <v>72.35</v>
+        <v>61.43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B30" t="n">
-        <v>66.67</v>
+        <v>54.55</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>445512</v>
+        <v>231453</v>
       </c>
       <c r="E30" t="n">
-        <v>3.36</v>
+        <v>1.74</v>
       </c>
       <c r="F30" t="n">
-        <v>3.36</v>
+        <v>1.74</v>
       </c>
       <c r="G30" t="n">
-        <v>75.71</v>
+        <v>63.17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B31" t="n">
-        <v>70</v>
+        <v>55.56</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>209985</v>
+        <v>226334</v>
       </c>
       <c r="E31" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="F31" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="G31" t="n">
-        <v>77.29</v>
+        <v>64.88</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B32" t="n">
-        <v>71.43</v>
+        <v>57.14</v>
       </c>
       <c r="C32" t="s">
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>171704</v>
+        <v>204906</v>
       </c>
       <c r="E32" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="F32" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="G32" t="n">
-        <v>78.59</v>
+        <v>66.42</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B33" t="n">
-        <v>72.73</v>
+        <v>60</v>
       </c>
       <c r="C33" t="s">
         <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>208040</v>
+        <v>360984</v>
       </c>
       <c r="E33" t="n">
-        <v>1.57</v>
+        <v>2.72</v>
       </c>
       <c r="F33" t="n">
-        <v>1.57</v>
+        <v>2.72</v>
       </c>
       <c r="G33" t="n">
-        <v>80.15</v>
+        <v>69.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B34" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>285372</v>
+        <v>211198</v>
       </c>
       <c r="E34" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="F34" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="G34" t="n">
-        <v>82.3</v>
+        <v>70.73</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B35" t="n">
-        <v>77.78</v>
+        <v>63.64</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>165175</v>
+        <v>214916</v>
       </c>
       <c r="E35" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="F35" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="G35" t="n">
-        <v>83.55</v>
+        <v>72.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B36" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
       </c>
       <c r="D36" t="n">
-        <v>295424</v>
+        <v>445512</v>
       </c>
       <c r="E36" t="n">
-        <v>2.23</v>
+        <v>3.36</v>
       </c>
       <c r="F36" t="n">
-        <v>2.23</v>
+        <v>3.36</v>
       </c>
       <c r="G36" t="n">
-        <v>85.78</v>
+        <v>75.71</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B37" t="n">
-        <v>81.82</v>
+        <v>70</v>
       </c>
       <c r="C37" t="s">
         <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>167006</v>
+        <v>209985</v>
       </c>
       <c r="E37" t="n">
-        <v>1.26</v>
+        <v>1.58</v>
       </c>
       <c r="F37" t="n">
-        <v>1.26</v>
+        <v>1.58</v>
       </c>
       <c r="G37" t="n">
-        <v>87.03</v>
+        <v>77.29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B38" t="n">
-        <v>83.33</v>
+        <v>71.43</v>
       </c>
       <c r="C38" t="s">
         <v>8</v>
       </c>
       <c r="D38" t="n">
-        <v>142050</v>
+        <v>171704</v>
       </c>
       <c r="E38" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="F38" t="n">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="G38" t="n">
-        <v>88.1</v>
+        <v>78.59</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B39" t="n">
-        <v>85.71</v>
+        <v>72.73</v>
       </c>
       <c r="C39" t="s">
         <v>8</v>
       </c>
       <c r="D39" t="n">
-        <v>131952</v>
+        <v>208040</v>
       </c>
       <c r="E39" t="n">
-        <v>0.99</v>
+        <v>1.57</v>
       </c>
       <c r="F39" t="n">
-        <v>0.99</v>
+        <v>1.57</v>
       </c>
       <c r="G39" t="n">
-        <v>89.1</v>
+        <v>80.15</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B40" t="n">
-        <v>87.5</v>
+        <v>75</v>
       </c>
       <c r="C40" t="s">
         <v>8</v>
       </c>
       <c r="D40" t="n">
-        <v>130625</v>
+        <v>285372</v>
       </c>
       <c r="E40" t="n">
-        <v>0.98</v>
+        <v>2.15</v>
       </c>
       <c r="F40" t="n">
-        <v>0.98</v>
+        <v>2.15</v>
       </c>
       <c r="G40" t="n">
-        <v>90.08</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B41" t="n">
-        <v>88.89</v>
+        <v>77.78</v>
       </c>
       <c r="C41" t="s">
         <v>8</v>
       </c>
       <c r="D41" t="n">
-        <v>123268</v>
+        <v>165175</v>
       </c>
       <c r="E41" t="n">
-        <v>0.93</v>
+        <v>1.24</v>
       </c>
       <c r="F41" t="n">
-        <v>0.93</v>
+        <v>1.24</v>
       </c>
       <c r="G41" t="n">
-        <v>91.01</v>
+        <v>83.55</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B42" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C42" t="s">
         <v>8</v>
       </c>
       <c r="D42" t="n">
-        <v>135809</v>
+        <v>295424</v>
       </c>
       <c r="E42" t="n">
-        <v>1.02</v>
+        <v>2.23</v>
       </c>
       <c r="F42" t="n">
-        <v>1.02</v>
+        <v>2.23</v>
       </c>
       <c r="G42" t="n">
-        <v>92.04</v>
+        <v>85.78</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B43" t="n">
-        <v>90.91</v>
+        <v>81.82</v>
       </c>
       <c r="C43" t="s">
         <v>8</v>
       </c>
       <c r="D43" t="n">
-        <v>138125</v>
+        <v>167006</v>
       </c>
       <c r="E43" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="F43" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="G43" t="n">
-        <v>93.08</v>
+        <v>87.03</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="2" t="n">
-        <v>918924</v>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>100</v>
+      <c r="A44" t="s">
+        <v>10</v>
+      </c>
+      <c r="B44" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>142050</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G44" t="n">
+        <v>88.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>85.71</v>
       </c>
       <c r="C45" t="s">
         <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>4140827</v>
+        <v>131952</v>
       </c>
       <c r="E45" t="n">
-        <v>31.59</v>
+        <v>0.99</v>
       </c>
       <c r="F45" t="n">
-        <v>31.59</v>
+        <v>0.99</v>
       </c>
       <c r="G45" t="n">
-        <v>31.59</v>
+        <v>89.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B46" t="n">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="C46" t="s">
         <v>8</v>
       </c>
       <c r="D46" t="n">
-        <v>5574634</v>
+        <v>130625</v>
       </c>
       <c r="E46" t="n">
-        <v>42.52</v>
+        <v>0.98</v>
       </c>
       <c r="F46" t="n">
-        <v>42.52</v>
+        <v>0.98</v>
       </c>
       <c r="G46" t="n">
-        <v>74.11</v>
+        <v>90.08</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="2" t="n">
-        <v>3394070</v>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>100</v>
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" t="n">
+        <v>88.89</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" t="n">
+        <v>123268</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G47" t="n">
+        <v>91.01</v>
       </c>
     </row>
     <row r="48">
@@ -1607,22 +1607,22 @@
         <v>10</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C48" t="s">
         <v>8</v>
       </c>
       <c r="D48" t="n">
-        <v>10297783</v>
+        <v>135809</v>
       </c>
       <c r="E48" t="n">
-        <v>77.59</v>
+        <v>1.02</v>
       </c>
       <c r="F48" t="n">
-        <v>77.59</v>
+        <v>1.02</v>
       </c>
       <c r="G48" t="n">
-        <v>77.59</v>
+        <v>92.04</v>
       </c>
     </row>
     <row r="49">
@@ -1630,22 +1630,22 @@
         <v>10</v>
       </c>
       <c r="B49" t="n">
-        <v>50</v>
+        <v>90.91</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>1763276</v>
+        <v>138125</v>
       </c>
       <c r="E49" t="n">
-        <v>13.29</v>
+        <v>1.04</v>
       </c>
       <c r="F49" t="n">
-        <v>13.29</v>
+        <v>1.04</v>
       </c>
       <c r="G49" t="n">
-        <v>90.88</v>
+        <v>93.08</v>
       </c>
     </row>
     <row r="50">
@@ -1659,13 +1659,13 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1211052</v>
+        <v>918924</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>9.12</v>
+        <v>6.92</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>9.12</v>
+        <v>6.92</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>100</v>
